--- a/docs/oc-regiones/pasajes-aereos-nacionales/los-rios.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M521"/>
+  <dimension ref="A1:M525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>245.7</v>
+        <v>243.62</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1099.38</v>
+        <v>1090.07</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>230.27</v>
+        <v>228.32</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>549.6900000000001</v>
+        <v>545.03</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>267.65</v>
+        <v>265.38</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>257.21</v>
+        <v>255.89</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1527.83</v>
+        <v>1519.98</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>218.59</v>
+        <v>217.47</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>141.49</v>
+        <v>140.08</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>300.66</v>
+        <v>297.66</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>110.23</v>
+        <v>109.07</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>177.23</v>
+        <v>175.38</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>487.76</v>
+        <v>482.65</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>394.07</v>
+        <v>389.94</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>158</v>
+        <v>156.34</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>309.07</v>
+        <v>305.83</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>445.12</v>
+        <v>440.45</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>614.49</v>
+        <v>611.13</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>419.98</v>
+        <v>417.68</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>512.48</v>
+        <v>509.68</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>445.12</v>
+        <v>442.68</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>211.24</v>
+        <v>210.08</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>175.15</v>
+        <v>173.2</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>374.09</v>
+        <v>369.93</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>221.96</v>
+        <v>219.49</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>624.8200000000001</v>
+        <v>617.86</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>85.54000000000001</v>
+        <v>85.06999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>284</v>
+        <v>282.44</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>197.43</v>
+        <v>196.35</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>333.7</v>
+        <v>331.88</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>479.64</v>
+        <v>479.03</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>142.61</v>
+        <v>142.43</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>98.69</v>
+        <v>98.56999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>81.48</v>
+        <v>81.38</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>66.08</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1013.25</v>
+        <v>1016.86</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>250.34</v>
+        <v>251.23</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>108.09</v>
+        <v>108.47</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1154.92</v>
+        <v>1159.04</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>108.2</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>257.01</v>
+        <v>257.93</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>82.5</v>
+        <v>82.79000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>112.42</v>
+        <v>112.82</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>314.35</v>
+        <v>315.48</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>147.74</v>
+        <v>149.35</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>200.7</v>
+        <v>202.89</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>291.25</v>
+        <v>294.41</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>457.72</v>
+        <v>462.7</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>222.56</v>
+        <v>224.98</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>179.54</v>
+        <v>181.49</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>243.86</v>
+        <v>246.51</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>176.22</v>
+        <v>178.13</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>108.09</v>
+        <v>109.26</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>238.87</v>
+        <v>241.47</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>231.25</v>
+        <v>233.77</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>255.63</v>
+        <v>256.47</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>356.43</v>
+        <v>357.6</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>153.19</v>
+        <v>153.69</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>108.09</v>
+        <v>108.44</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>392.24</v>
+        <v>393.53</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>73.05</v>
+        <v>73.29000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>556.46</v>
+        <v>566.0599999999999</v>
       </c>
     </row>
     <row r="64">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>268.61</v>
+        <v>273.25</v>
       </c>
     </row>
     <row r="65">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>402.56</v>
+        <v>405.35</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>159.12</v>
+        <v>160.22</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>453.29</v>
+        <v>456.55</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>205.3</v>
+        <v>206.78</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>304.68</v>
+        <v>306.88</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>286.95</v>
+        <v>289.01</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>520.67</v>
+        <v>524.4299999999999</v>
       </c>
     </row>
     <row r="72">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>383.22</v>
+        <v>385.98</v>
       </c>
     </row>
     <row r="73">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>260.34</v>
+        <v>262.21</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>191.61</v>
+        <v>192.99</v>
       </c>
     </row>
     <row r="75">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>243.47</v>
+        <v>243.04</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>424.81</v>
+        <v>424.06</v>
       </c>
     </row>
     <row r="77">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>225.86</v>
+        <v>225.46</v>
       </c>
     </row>
     <row r="78">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>175.1</v>
+        <v>174.38</v>
       </c>
     </row>
     <row r="79">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>365.92</v>
+        <v>364.42</v>
       </c>
     </row>
     <row r="80">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>152.71</v>
+        <v>152.08</v>
       </c>
     </row>
     <row r="81">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>77.26000000000001</v>
+        <v>76.94</v>
       </c>
     </row>
     <row r="82">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>122.47</v>
+        <v>121.96</v>
       </c>
     </row>
     <row r="83">
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>112.7</v>
+        <v>112.52</v>
       </c>
     </row>
     <row r="84">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>101.45</v>
+        <v>101.29</v>
       </c>
     </row>
     <row r="85">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>97.78</v>
+        <v>97.63</v>
       </c>
     </row>
     <row r="86">
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>220.29</v>
+        <v>219.95</v>
       </c>
     </row>
     <row r="87">
@@ -5762,7 +5762,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>114.13</v>
+        <v>113.96</v>
       </c>
     </row>
     <row r="88">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>248.35</v>
+        <v>247.97</v>
       </c>
     </row>
     <row r="89">
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>211.38</v>
+        <v>212.47</v>
       </c>
     </row>
     <row r="90">
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>357.16</v>
+        <v>359</v>
       </c>
     </row>
     <row r="91">
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>147.74</v>
+        <v>148.78</v>
       </c>
     </row>
     <row r="92">
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>115.95</v>
+        <v>116.77</v>
       </c>
     </row>
     <row r="93">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>130.21</v>
+        <v>131.13</v>
       </c>
     </row>
     <row r="94">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>122.04</v>
+        <v>122.91</v>
       </c>
     </row>
     <row r="95">
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>267.12</v>
+        <v>263.66</v>
       </c>
     </row>
     <row r="96">
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>140.44</v>
+        <v>138.63</v>
       </c>
     </row>
     <row r="97">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>300.15</v>
+        <v>297.17</v>
       </c>
     </row>
     <row r="98">
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>112.09</v>
+        <v>111.69</v>
       </c>
     </row>
     <row r="99">
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>423.92</v>
+        <v>422.4</v>
       </c>
     </row>
     <row r="100">
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>299.16</v>
+        <v>298.08</v>
       </c>
     </row>
     <row r="101">
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>147.67</v>
+        <v>147.14</v>
       </c>
     </row>
     <row r="102">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>123.3</v>
+        <v>122.86</v>
       </c>
     </row>
     <row r="103">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>97.84</v>
+        <v>97.48999999999999</v>
       </c>
     </row>
     <row r="104">
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>147.44</v>
+        <v>146.92</v>
       </c>
     </row>
     <row r="105">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>135.28</v>
+        <v>134.99</v>
       </c>
     </row>
     <row r="106">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>105.41</v>
+        <v>105.18</v>
       </c>
     </row>
     <row r="107">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>204.79</v>
+        <v>204.34</v>
       </c>
     </row>
     <row r="108">
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>172.3</v>
+        <v>171.93</v>
       </c>
     </row>
     <row r="109">
@@ -7104,7 +7104,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>301.78</v>
+        <v>300.52</v>
       </c>
     </row>
     <row r="110">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>150.62</v>
+        <v>149.99</v>
       </c>
     </row>
     <row r="111">
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>413.91</v>
+        <v>409.12</v>
       </c>
     </row>
     <row r="112">
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>5.44</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="113">
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>329.14</v>
+        <v>326.35</v>
       </c>
     </row>
     <row r="114">
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>292.08</v>
+        <v>291.85</v>
       </c>
     </row>
     <row r="115">
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>770.36</v>
+        <v>773.3200000000001</v>
       </c>
     </row>
     <row r="116">
@@ -7535,7 +7535,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>111.3</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="117">
@@ -7596,7 +7596,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>861.61</v>
+        <v>865.52</v>
       </c>
     </row>
     <row r="118">
@@ -7657,7 +7657,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>163.67</v>
+        <v>164.11</v>
       </c>
     </row>
     <row r="119">
@@ -7718,7 +7718,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>371.85</v>
+        <v>371.33</v>
       </c>
     </row>
     <row r="120">
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>714.27</v>
+        <v>715.1900000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>229.93</v>
+        <v>231.9</v>
       </c>
     </row>
     <row r="122">
@@ -7901,7 +7901,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>168.51</v>
+        <v>170.58</v>
       </c>
     </row>
     <row r="123">
@@ -7962,7 +7962,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>907.71</v>
+        <v>918.86</v>
       </c>
     </row>
     <row r="124">
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>547.47</v>
+        <v>554.2</v>
       </c>
     </row>
     <row r="125">
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>237.06</v>
+        <v>231.01</v>
       </c>
     </row>
     <row r="126">
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>113.28</v>
+        <v>111.07</v>
       </c>
     </row>
     <row r="127">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>69.56999999999999</v>
+        <v>68.20999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>670.23</v>
+        <v>654.55</v>
       </c>
     </row>
     <row r="129">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>443.43</v>
+        <v>433.06</v>
       </c>
     </row>
     <row r="130">
@@ -8389,7 +8389,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>98.02</v>
+        <v>95.73</v>
       </c>
     </row>
     <row r="131">
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>62.61</v>
+        <v>61.14</v>
       </c>
     </row>
     <row r="132">
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>352.51</v>
+        <v>348.03</v>
       </c>
     </row>
     <row r="133">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>138.23</v>
+        <v>136.47</v>
       </c>
     </row>
     <row r="134">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>199.82</v>
+        <v>196.94</v>
       </c>
     </row>
     <row r="135">
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>988.11</v>
+        <v>975.34</v>
       </c>
     </row>
     <row r="136">
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>507.72</v>
+        <v>501.16</v>
       </c>
     </row>
     <row r="137">
@@ -8816,7 +8816,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>541.84</v>
+        <v>534.83</v>
       </c>
     </row>
     <row r="138">
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>221.73</v>
+        <v>221.29</v>
       </c>
     </row>
     <row r="139">
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>119.34</v>
+        <v>119.11</v>
       </c>
     </row>
     <row r="140">
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>184.63</v>
+        <v>184.27</v>
       </c>
     </row>
     <row r="141">
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>190.26</v>
+        <v>189.89</v>
       </c>
     </row>
     <row r="142">
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>62.61</v>
+        <v>62.49</v>
       </c>
     </row>
     <row r="143">
@@ -9182,7 +9182,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>139.94</v>
+        <v>139.67</v>
       </c>
     </row>
     <row r="144">
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>278.3</v>
+        <v>277.75</v>
       </c>
     </row>
     <row r="145">
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>251.77</v>
+        <v>252.12</v>
       </c>
     </row>
     <row r="147">
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>76.58</v>
+        <v>76.69</v>
       </c>
     </row>
     <row r="148">
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>315.91</v>
+        <v>315.69</v>
       </c>
     </row>
     <row r="149">
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>134.57</v>
+        <v>134.48</v>
       </c>
     </row>
     <row r="150">
@@ -9609,7 +9609,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>76.58</v>
+        <v>76.53</v>
       </c>
     </row>
     <row r="151">
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>119.3</v>
+        <v>119.22</v>
       </c>
     </row>
     <row r="152">
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>119.3</v>
+        <v>118.89</v>
       </c>
     </row>
     <row r="153">
@@ -9792,7 +9792,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>69.06</v>
+        <v>68.81999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>148.29</v>
+        <v>147.79</v>
       </c>
     </row>
     <row r="155">
@@ -9914,7 +9914,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>163.36</v>
+        <v>162.8</v>
       </c>
     </row>
     <row r="156">
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>162.32</v>
+        <v>161.76</v>
       </c>
     </row>
     <row r="157">
@@ -10036,7 +10036,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>279.85</v>
+        <v>278.37</v>
       </c>
     </row>
     <row r="158">
@@ -10097,7 +10097,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>283.05</v>
+        <v>281.56</v>
       </c>
     </row>
     <row r="159">
@@ -10158,7 +10158,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>279.57</v>
+        <v>278.1</v>
       </c>
     </row>
     <row r="160">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>131.01</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="161">
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>299.09</v>
+        <v>301.05</v>
       </c>
     </row>
     <row r="162">
@@ -10341,7 +10341,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>249.62</v>
+        <v>251.25</v>
       </c>
     </row>
     <row r="163">
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1129.22</v>
+        <v>1144.43</v>
       </c>
     </row>
     <row r="164">
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>174.45</v>
+        <v>177.11</v>
       </c>
     </row>
     <row r="165">
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>159.51</v>
+        <v>163.39</v>
       </c>
     </row>
     <row r="166">
@@ -10585,7 +10585,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>107.85</v>
+        <v>110.47</v>
       </c>
     </row>
     <row r="167">
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>327.73</v>
+        <v>336.02</v>
       </c>
     </row>
     <row r="168">
@@ -10707,7 +10707,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>308.15</v>
+        <v>315.94</v>
       </c>
     </row>
     <row r="169">
@@ -10768,7 +10768,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>465.95</v>
+        <v>477.73</v>
       </c>
     </row>
     <row r="170">
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>171.13</v>
+        <v>176.31</v>
       </c>
     </row>
     <row r="171">
@@ -10890,7 +10890,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>230.15</v>
+        <v>237.13</v>
       </c>
     </row>
     <row r="172">
@@ -10951,7 +10951,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>413.99</v>
+        <v>412.51</v>
       </c>
     </row>
     <row r="173">
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>106.67</v>
+        <v>106.29</v>
       </c>
     </row>
     <row r="174">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>454.75</v>
+        <v>451.35</v>
       </c>
     </row>
     <row r="175">
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>112.67</v>
+        <v>111.83</v>
       </c>
     </row>
     <row r="176">
@@ -11195,7 +11195,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>195.88</v>
+        <v>194.41</v>
       </c>
     </row>
     <row r="177">
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>284.45</v>
+        <v>285.23</v>
       </c>
     </row>
     <row r="178">
@@ -11317,7 +11317,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>199.71</v>
+        <v>200.26</v>
       </c>
     </row>
     <row r="179">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>247.39</v>
+        <v>249.02</v>
       </c>
     </row>
     <row r="180">
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>196.64</v>
+        <v>198.39</v>
       </c>
     </row>
     <row r="181">
@@ -11500,7 +11500,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>437.82</v>
+        <v>441.72</v>
       </c>
     </row>
     <row r="182">
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>340.98</v>
+        <v>344.02</v>
       </c>
     </row>
     <row r="183">
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>294.74</v>
+        <v>297.37</v>
       </c>
     </row>
     <row r="184">
@@ -11683,7 +11683,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>382.53</v>
+        <v>381.87</v>
       </c>
     </row>
     <row r="185">
@@ -11744,7 +11744,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>104.04</v>
+        <v>103.86</v>
       </c>
     </row>
     <row r="186">
@@ -11805,7 +11805,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>237.64</v>
+        <v>237.4</v>
       </c>
     </row>
     <row r="187">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>199.71</v>
+        <v>198.28</v>
       </c>
     </row>
     <row r="188">
@@ -11927,7 +11927,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>248.78</v>
+        <v>247</v>
       </c>
     </row>
     <row r="189">
@@ -11988,7 +11988,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>77.95</v>
+        <v>77.39</v>
       </c>
     </row>
     <row r="190">
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>222.2</v>
+        <v>220.6</v>
       </c>
     </row>
     <row r="191">
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>492.87</v>
+        <v>492.14</v>
       </c>
     </row>
     <row r="192">
@@ -12171,7 +12171,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>322.91</v>
+        <v>321.15</v>
       </c>
     </row>
     <row r="193">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>233.06</v>
+        <v>231.69</v>
       </c>
     </row>
     <row r="194">
@@ -12293,7 +12293,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>536.1799999999999</v>
+        <v>532.92</v>
       </c>
     </row>
     <row r="195">
@@ -12354,7 +12354,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>505.05</v>
+        <v>503.1</v>
       </c>
     </row>
     <row r="196">
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>241.4</v>
+        <v>242.65</v>
       </c>
     </row>
     <row r="197">
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>169.5</v>
+        <v>170.37</v>
       </c>
     </row>
     <row r="198">
@@ -12537,7 +12537,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>313.65</v>
+        <v>315.27</v>
       </c>
     </row>
     <row r="199">
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>268.8</v>
+        <v>269.06</v>
       </c>
     </row>
     <row r="200">
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>216.48</v>
+        <v>216.69</v>
       </c>
     </row>
     <row r="201">
@@ -12720,7 +12720,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>375.47</v>
+        <v>392.06</v>
       </c>
     </row>
     <row r="202">
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>200.91</v>
+        <v>206.75</v>
       </c>
     </row>
     <row r="203">
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>290.03</v>
+        <v>298.45</v>
       </c>
     </row>
     <row r="204">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>183.27</v>
+        <v>183.99</v>
       </c>
     </row>
     <row r="205">
@@ -12964,7 +12964,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>166.68</v>
+        <v>169.43</v>
       </c>
     </row>
     <row r="206">
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>292.79</v>
+        <v>297.62</v>
       </c>
     </row>
     <row r="207">
@@ -13086,7 +13086,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>233.65</v>
+        <v>237.5</v>
       </c>
     </row>
     <row r="208">
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>92.38</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="209">
@@ -13208,7 +13208,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>629.41</v>
+        <v>630.96</v>
       </c>
     </row>
     <row r="210">
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>78.34</v>
+        <v>77.33</v>
       </c>
     </row>
     <row r="211">
@@ -13330,7 +13330,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>99.95</v>
+        <v>98.66</v>
       </c>
     </row>
     <row r="212">
@@ -13391,7 +13391,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>445.77</v>
+        <v>440.03</v>
       </c>
     </row>
     <row r="213">
@@ -13452,7 +13452,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>115.4</v>
+        <v>114.59</v>
       </c>
     </row>
     <row r="214">
@@ -13513,7 +13513,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>204.35</v>
+        <v>208.06</v>
       </c>
     </row>
     <row r="215">
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>156.56</v>
+        <v>159.4</v>
       </c>
     </row>
     <row r="216">
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>758.99</v>
+        <v>772.76</v>
       </c>
     </row>
     <row r="217">
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>69.51000000000001</v>
+        <v>70.78</v>
       </c>
     </row>
     <row r="218">
@@ -13757,7 +13757,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>72.87</v>
+        <v>74.19</v>
       </c>
     </row>
     <row r="219">
@@ -13818,7 +13818,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>177.83</v>
+        <v>180.61</v>
       </c>
     </row>
     <row r="220">
@@ -13879,7 +13879,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>520.83</v>
+        <v>520.8099999999999</v>
       </c>
     </row>
     <row r="221">
@@ -13940,7 +13940,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>78.81</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="222">
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>73.36</v>
+        <v>73.03</v>
       </c>
     </row>
     <row r="223">
@@ -14062,7 +14062,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>258.83</v>
+        <v>259.05</v>
       </c>
     </row>
     <row r="224">
@@ -14123,7 +14123,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>258.83</v>
+        <v>259.05</v>
       </c>
     </row>
     <row r="225">
@@ -14184,7 +14184,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>80.62</v>
+        <v>80.95</v>
       </c>
     </row>
     <row r="226">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>126.05</v>
+        <v>126.57</v>
       </c>
     </row>
     <row r="227">
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>69.18000000000001</v>
+        <v>68.98999999999999</v>
       </c>
     </row>
     <row r="228">
@@ -14367,7 +14367,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>192</v>
+        <v>191.47</v>
       </c>
     </row>
     <row r="229">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>464.24</v>
+        <v>462.96</v>
       </c>
     </row>
     <row r="230">
@@ -14489,7 +14489,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>324.71</v>
+        <v>323.81</v>
       </c>
     </row>
     <row r="231">
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>262.93</v>
+        <v>261.42</v>
       </c>
     </row>
     <row r="232">
@@ -14615,7 +14615,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>371.14</v>
+        <v>368.76</v>
       </c>
     </row>
     <row r="233">
@@ -14676,7 +14676,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>194.78</v>
+        <v>193.54</v>
       </c>
     </row>
     <row r="234">
@@ -14737,7 +14737,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>943.29</v>
+        <v>929.64</v>
       </c>
     </row>
     <row r="235">
@@ -14798,7 +14798,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>140.6</v>
+        <v>137.58</v>
       </c>
     </row>
     <row r="236">
@@ -14859,7 +14859,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>223.33</v>
+        <v>218.13</v>
       </c>
     </row>
     <row r="237">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>80.11</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="238">
@@ -14981,7 +14981,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>129.03</v>
+        <v>126.03</v>
       </c>
     </row>
     <row r="239">
@@ -15042,7 +15042,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>163.48</v>
+        <v>159.68</v>
       </c>
     </row>
     <row r="240">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>102.97</v>
+        <v>100.57</v>
       </c>
     </row>
     <row r="241">
@@ -15164,7 +15164,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>127.94</v>
+        <v>124.96</v>
       </c>
     </row>
     <row r="242">
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>514.08</v>
+        <v>502.12</v>
       </c>
     </row>
     <row r="243">
@@ -15286,7 +15286,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>153.59</v>
+        <v>150.02</v>
       </c>
     </row>
     <row r="244">
@@ -15347,7 +15347,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>332.62</v>
+        <v>324.88</v>
       </c>
     </row>
     <row r="245">
@@ -15408,7 +15408,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>223.78</v>
+        <v>216.65</v>
       </c>
     </row>
     <row r="246">
@@ -15469,7 +15469,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>216.79</v>
+        <v>212.51</v>
       </c>
     </row>
     <row r="247">
@@ -15530,7 +15530,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>81.19</v>
+        <v>79.58</v>
       </c>
     </row>
     <row r="248">
@@ -15591,7 +15591,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>225.14</v>
+        <v>220.7</v>
       </c>
     </row>
     <row r="249">
@@ -15652,7 +15652,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>328.05</v>
+        <v>321.58</v>
       </c>
     </row>
     <row r="250">
@@ -15713,7 +15713,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>67.98999999999999</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="251">
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>207.09</v>
+        <v>201.64</v>
       </c>
     </row>
     <row r="252">
@@ -15835,7 +15835,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>154.47</v>
+        <v>150.4</v>
       </c>
     </row>
     <row r="253">
@@ -15896,7 +15896,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>62.76</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="254">
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>325.32</v>
+        <v>316.76</v>
       </c>
     </row>
     <row r="255">
@@ -16018,7 +16018,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>240.24</v>
+        <v>233.8</v>
       </c>
     </row>
     <row r="256">
@@ -16079,7 +16079,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>208.27</v>
+        <v>202.69</v>
       </c>
     </row>
     <row r="257">
@@ -16140,13 +16140,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>476.33</v>
+        <v>463.58</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>926853-5-CM26</t>
+          <t>2281-467-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16171,12 +16171,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16186,12 +16186,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -16201,13 +16201,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>387.47</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2281-467-CM26</t>
+          <t>2281-466-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16262,13 +16262,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>86.48</v>
+        <v>188.31</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2281-466-CM26</t>
+          <t>926853-5-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>Zona de Bienestar Valdivia</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16308,12 +16308,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -16323,13 +16323,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>187.76</v>
+        <v>388.6</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>5740-107-CM26</t>
+          <t>2281-464-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16354,12 +16354,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16384,13 +16384,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>197.45</v>
+        <v>372.94</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2281-464-CM26</t>
+          <t>5740-107-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16415,12 +16415,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>371.86</v>
+        <v>198.02</v>
       </c>
     </row>
     <row r="263">
@@ -16506,7 +16506,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>275.86</v>
+        <v>276.67</v>
       </c>
     </row>
     <row r="264">
@@ -16567,7 +16567,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>511.36</v>
+        <v>513.48</v>
       </c>
     </row>
     <row r="265">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>189.7</v>
+        <v>190.49</v>
       </c>
     </row>
     <row r="266">
@@ -16689,7 +16689,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>198.77</v>
+        <v>200.45</v>
       </c>
     </row>
     <row r="267">
@@ -16750,7 +16750,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>141.78</v>
+        <v>142.99</v>
       </c>
     </row>
     <row r="268">
@@ -16811,7 +16811,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>258.39</v>
+        <v>260.59</v>
       </c>
     </row>
     <row r="269">
@@ -16872,7 +16872,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>325.55</v>
+        <v>328.31</v>
       </c>
     </row>
     <row r="270">
@@ -16933,13 +16933,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>390.06</v>
+        <v>393.37</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>5418-73-CM26</t>
+          <t>5418-72-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16994,7 +16994,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>232.73</v>
+        <v>232.34</v>
       </c>
     </row>
     <row r="272">
@@ -17055,7 +17055,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>232.73</v>
+        <v>232.34</v>
       </c>
     </row>
     <row r="273">
@@ -17116,13 +17116,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>232.73</v>
+        <v>232.34</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>5418-72-CM26</t>
+          <t>5418-73-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17177,7 +17177,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>232.73</v>
+        <v>232.34</v>
       </c>
     </row>
     <row r="275">
@@ -17238,7 +17238,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>112.85</v>
+        <v>112.66</v>
       </c>
     </row>
     <row r="276">
@@ -17299,7 +17299,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>140.82</v>
+        <v>140.59</v>
       </c>
     </row>
     <row r="277">
@@ -17360,7 +17360,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>1918.8</v>
+        <v>1915.59</v>
       </c>
     </row>
     <row r="278">
@@ -17421,7 +17421,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>255.94</v>
+        <v>259.09</v>
       </c>
     </row>
     <row r="279">
@@ -17482,7 +17482,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>251.39</v>
+        <v>254.49</v>
       </c>
     </row>
     <row r="280">
@@ -17543,7 +17543,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>506.18</v>
+        <v>512.41</v>
       </c>
     </row>
     <row r="281">
@@ -17604,7 +17604,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>631.1</v>
+        <v>639.5</v>
       </c>
     </row>
     <row r="282">
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>436.61</v>
+        <v>442.42</v>
       </c>
     </row>
     <row r="283">
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>64.89</v>
+        <v>65.73999999999999</v>
       </c>
     </row>
     <row r="284">
@@ -17787,7 +17787,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>62.85</v>
+        <v>63.67</v>
       </c>
     </row>
     <row r="285">
@@ -17848,7 +17848,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>64.89</v>
+        <v>66.48999999999999</v>
       </c>
     </row>
     <row r="286">
@@ -17909,7 +17909,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>95.93000000000001</v>
+        <v>98.29000000000001</v>
       </c>
     </row>
     <row r="287">
@@ -17970,7 +17970,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>107.04</v>
+        <v>109.68</v>
       </c>
     </row>
     <row r="288">
@@ -18031,7 +18031,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>481.49</v>
+        <v>493.34</v>
       </c>
     </row>
     <row r="289">
@@ -18092,7 +18092,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>459.89</v>
+        <v>471.21</v>
       </c>
     </row>
     <row r="290">
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>250.8</v>
+        <v>256.97</v>
       </c>
     </row>
     <row r="291">
@@ -18214,7 +18214,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>248.08</v>
+        <v>252.77</v>
       </c>
     </row>
     <row r="292">
@@ -18275,7 +18275,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>570.37</v>
+        <v>581.15</v>
       </c>
     </row>
     <row r="293">
@@ -18336,7 +18336,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>120.19</v>
+        <v>122.47</v>
       </c>
     </row>
     <row r="294">
@@ -18397,7 +18397,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>122.99</v>
+        <v>125.31</v>
       </c>
     </row>
     <row r="295">
@@ -18458,7 +18458,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>224.02</v>
+        <v>228.26</v>
       </c>
     </row>
     <row r="296">
@@ -18519,7 +18519,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1103.16</v>
+        <v>1113.1</v>
       </c>
     </row>
     <row r="297">
@@ -18580,7 +18580,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>586.36</v>
+        <v>590.11</v>
       </c>
     </row>
     <row r="298">
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>196.16</v>
+        <v>197.42</v>
       </c>
     </row>
     <row r="299">
@@ -18702,7 +18702,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>295.91</v>
+        <v>297.8</v>
       </c>
     </row>
     <row r="300">
@@ -18763,7 +18763,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>479.65</v>
+        <v>482.72</v>
       </c>
     </row>
     <row r="301">
@@ -18824,7 +18824,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>233.04</v>
+        <v>234.53</v>
       </c>
     </row>
     <row r="302">
@@ -18885,7 +18885,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>245.83</v>
+        <v>247.41</v>
       </c>
     </row>
     <row r="303">
@@ -18946,7 +18946,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>200.04</v>
+        <v>200.66</v>
       </c>
     </row>
     <row r="304">
@@ -19007,7 +19007,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>127.79</v>
+        <v>128.2</v>
       </c>
     </row>
     <row r="305">
@@ -19068,7 +19068,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>127.79</v>
+        <v>128.2</v>
       </c>
     </row>
     <row r="306">
@@ -19133,7 +19133,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>45.5</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="307">
@@ -19194,7 +19194,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>500.59</v>
+        <v>502.66</v>
       </c>
     </row>
     <row r="308">
@@ -19255,7 +19255,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>140.12</v>
+        <v>140.41</v>
       </c>
     </row>
     <row r="309">
@@ -19316,7 +19316,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>122.99</v>
+        <v>123.24</v>
       </c>
     </row>
     <row r="310">
@@ -19377,7 +19377,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>200.7</v>
+        <v>199.84</v>
       </c>
     </row>
     <row r="311">
@@ -19438,7 +19438,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>200.7</v>
+        <v>199.84</v>
       </c>
     </row>
     <row r="312">
@@ -19499,7 +19499,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>388.35</v>
+        <v>386.68</v>
       </c>
     </row>
     <row r="313">
@@ -19560,7 +19560,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>66.95</v>
+        <v>66.66</v>
       </c>
     </row>
     <row r="314">
@@ -19621,7 +19621,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>122.99</v>
+        <v>122.46</v>
       </c>
     </row>
     <row r="315">
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>53.27</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="316">
@@ -19743,7 +19743,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>51.17</v>
+        <v>50.47</v>
       </c>
     </row>
     <row r="317">
@@ -19804,7 +19804,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>127.83</v>
+        <v>126.74</v>
       </c>
     </row>
     <row r="318">
@@ -19865,7 +19865,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>172.15</v>
+        <v>170.68</v>
       </c>
     </row>
     <row r="319">
@@ -19926,7 +19926,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>153.9</v>
+        <v>154.73</v>
       </c>
     </row>
     <row r="320">
@@ -19987,7 +19987,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>95.04000000000001</v>
+        <v>95.55</v>
       </c>
     </row>
     <row r="321">
@@ -20048,13 +20048,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>118.01</v>
+        <v>118.65</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1422032-32-CM26</t>
+          <t>3762-372-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20074,17 +20074,17 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20094,12 +20094,12 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K322" t="inlineStr"/>
@@ -20109,13 +20109,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>257.17</v>
+        <v>78.48999999999999</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>3762-372-CM26</t>
+          <t>1422032-32-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20135,17 +20135,17 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20155,12 +20155,12 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K323" t="inlineStr"/>
@@ -20170,7 +20170,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>77.63</v>
+        <v>260.04</v>
       </c>
     </row>
     <row r="324">
@@ -20231,7 +20231,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>229.61</v>
+        <v>230.48</v>
       </c>
     </row>
     <row r="325">
@@ -20292,13 +20292,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>158.42</v>
+        <v>159.02</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>780724-50-CM26</t>
+          <t>5740-156-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20323,12 +20323,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>61.980.330-2</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Ilustre Tercer Tribunal Ambiental</t>
+          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20353,13 +20353,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>275.64</v>
+        <v>118.46</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5740-156-CM26</t>
+          <t>780724-50-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20384,12 +20384,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>61.980.330-2</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>Ilustre Tercer Tribunal Ambiental</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>118.01</v>
+        <v>276.68</v>
       </c>
     </row>
     <row r="328">
@@ -20475,7 +20475,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>116</v>
+        <v>115.71</v>
       </c>
     </row>
     <row r="329">
@@ -20536,7 +20536,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>568.48</v>
+        <v>567.04</v>
       </c>
     </row>
     <row r="330">
@@ -20597,7 +20597,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>276.06</v>
+        <v>275.37</v>
       </c>
     </row>
     <row r="331">
@@ -20658,7 +20658,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>87.34</v>
+        <v>87.12</v>
       </c>
     </row>
     <row r="332">
@@ -20719,7 +20719,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>145.08</v>
+        <v>144.71</v>
       </c>
     </row>
     <row r="333">
@@ -20780,7 +20780,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>199.02</v>
+        <v>200.91</v>
       </c>
     </row>
     <row r="334">
@@ -20841,7 +20841,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>293.26</v>
+        <v>295.45</v>
       </c>
     </row>
     <row r="335">
@@ -20902,13 +20902,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>108.2</v>
+        <v>109</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1057547-7342-CM26</t>
+          <t>591376-40-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -20933,12 +20933,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>Instituto de Desarrollo Agropecuario</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -20963,13 +20963,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>412.07</v>
+        <v>81.19</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>591376-40-CM26</t>
+          <t>1107282-84-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -20989,17 +20989,17 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Instituto de Desarrollo Agropecuario</t>
+          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21024,13 +21024,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>82.01000000000001</v>
+        <v>52.31</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1107282-84-CM26</t>
+          <t>5661-25-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21055,12 +21055,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21070,12 +21070,12 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K338" t="inlineStr"/>
@@ -21085,13 +21085,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>52.84</v>
+        <v>319.66</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1107282-85-CM26</t>
+          <t>1057547-7342-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21111,17 +21111,17 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21131,12 +21131,12 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K339" t="inlineStr"/>
@@ -21146,13 +21146,13 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>197.63</v>
+        <v>407.96</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1107282-83-CM26</t>
+          <t>1035685-155-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21172,17 +21172,17 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21207,13 +21207,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>85.34</v>
+        <v>185.42</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1035685-155-CM26</t>
+          <t>1107282-83-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -21233,17 +21233,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21268,13 +21268,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>187.28</v>
+        <v>84.48999999999999</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1035685-154-CM26</t>
+          <t>1107282-85-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21294,17 +21294,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21314,12 +21314,12 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K342" t="inlineStr"/>
@@ -21329,13 +21329,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>123.02</v>
+        <v>195.66</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>5661-25-CM26</t>
+          <t>1035685-154-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21355,17 +21355,17 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21375,12 +21375,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K343" t="inlineStr"/>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>322.88</v>
+        <v>121.8</v>
       </c>
     </row>
     <row r="344">
@@ -21451,13 +21451,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>459.67</v>
+        <v>457.66</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>4777-417-CM26</t>
+          <t>299-78-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -21477,17 +21477,17 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -21512,13 +21512,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>271.44</v>
+        <v>151.43</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>299-78-CM26</t>
+          <t>5418-101-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -21543,12 +21543,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21573,13 +21573,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>153.1</v>
+        <v>1623.72</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>5418-101-CM26</t>
+          <t>1875-13-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -21604,12 +21604,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21634,13 +21634,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>1641.58</v>
+        <v>557.26</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1875-13-CM26</t>
+          <t>1035685-163-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -21665,12 +21665,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>60.704.000-1</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE TURISMO</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -21680,12 +21680,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K348" t="inlineStr"/>
@@ -21695,13 +21695,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>563.39</v>
+        <v>78.14</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1035685-162-CM26</t>
+          <t>1035685-164-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -21756,13 +21756,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>87.93000000000001</v>
+        <v>194.87</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1035685-163-CM26</t>
+          <t>1035685-165-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -21817,13 +21817,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>79</v>
+        <v>194.87</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1035685-164-CM26</t>
+          <t>4777-415-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -21843,17 +21843,17 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -21863,12 +21863,12 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K351" t="inlineStr"/>
@@ -21878,13 +21878,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>197.01</v>
+        <v>391.49</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1035685-165-CM26</t>
+          <t>4777-416-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -21904,17 +21904,17 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -21939,13 +21939,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>197.01</v>
+        <v>231.45</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>4777-415-CM26</t>
+          <t>4777-417-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -22000,13 +22000,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>395.8</v>
+        <v>268.49</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>4777-416-CM26</t>
+          <t>1035685-162-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -22026,17 +22026,17 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -22061,7 +22061,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>233.99</v>
+        <v>86.97</v>
       </c>
     </row>
     <row r="355">
@@ -22122,7 +22122,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>68.08</v>
+        <v>67.92</v>
       </c>
     </row>
     <row r="356">
@@ -22183,13 +22183,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>172.15</v>
+        <v>171.73</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>3762-425-CM26</t>
+          <t>3762-427-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -22229,12 +22229,12 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K357" t="inlineStr"/>
@@ -22244,13 +22244,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>80.11</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>3762-427-CM26</t>
+          <t>2281-712-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22275,12 +22275,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -22290,12 +22290,12 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K358" t="inlineStr"/>
@@ -22305,13 +22305,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>92.25</v>
+        <v>307.77</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>3762-428-CM26</t>
+          <t>3762-425-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -22366,13 +22366,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>100.31</v>
+        <v>80.51000000000001</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1035685-168-CM26</t>
+          <t>3762-428-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -22392,17 +22392,17 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -22412,12 +22412,12 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K360" t="inlineStr"/>
@@ -22427,13 +22427,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>74.98999999999999</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>5650-15-CM26</t>
+          <t>1035685-168-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -22458,12 +22458,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.402.010-5</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Regional Min.Bs.Nac. XIV Región Los Rios</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -22473,12 +22473,12 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K361" t="inlineStr"/>
@@ -22488,13 +22488,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>140.72</v>
+        <v>75.36</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1035685-166-CM26</t>
+          <t>5650-15-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -22519,12 +22519,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.402.010-5</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>Regional Min.Bs.Nac. XIV Región Los Rios</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -22534,12 +22534,12 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K362" t="inlineStr"/>
@@ -22549,13 +22549,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>125.73</v>
+        <v>141.41</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2281-713-CM26</t>
+          <t>1035685-166-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -22575,17 +22575,17 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -22595,12 +22595,12 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K363" t="inlineStr"/>
@@ -22610,13 +22610,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>236.74</v>
+        <v>126.35</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2281-712-CM26</t>
+          <t>2281-713-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -22671,7 +22671,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>306.27</v>
+        <v>237.9</v>
       </c>
     </row>
     <row r="365">
@@ -22732,7 +22732,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>110.08</v>
+        <v>110.62</v>
       </c>
     </row>
     <row r="366">
@@ -22793,7 +22793,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>241.6</v>
+        <v>242.4</v>
       </c>
     </row>
     <row r="367">
@@ -22854,7 +22854,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>478.24</v>
+        <v>479.83</v>
       </c>
     </row>
     <row r="368">
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>474.95</v>
+        <v>476.53</v>
       </c>
     </row>
     <row r="369">
@@ -22976,7 +22976,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>181.67</v>
+        <v>182.28</v>
       </c>
     </row>
     <row r="370">
@@ -23037,13 +23037,13 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>67.02</v>
+        <v>67.25</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2905-359-CM26</t>
+          <t>3762-432-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -23063,17 +23063,17 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -23098,13 +23098,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>142.52</v>
+        <v>198.97</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>3762-432-CM26</t>
+          <t>5418-107-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -23124,17 +23124,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -23159,13 +23159,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>198.31</v>
+        <v>473.67</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1422032-49-CM26</t>
+          <t>2905-359-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -23185,17 +23185,17 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -23205,12 +23205,12 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K373" t="inlineStr"/>
@@ -23220,7 +23220,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>84.01000000000001</v>
+        <v>143</v>
       </c>
     </row>
     <row r="374">
@@ -23281,7 +23281,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>325.65</v>
+        <v>326.73</v>
       </c>
     </row>
     <row r="375">
@@ -23342,7 +23342,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>138.16</v>
+        <v>138.61</v>
       </c>
     </row>
     <row r="376">
@@ -23403,7 +23403,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>207.72</v>
+        <v>208.41</v>
       </c>
     </row>
     <row r="377">
@@ -23464,7 +23464,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>136.17</v>
+        <v>136.62</v>
       </c>
     </row>
     <row r="378">
@@ -23525,7 +23525,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>107.03</v>
+        <v>107.39</v>
       </c>
     </row>
     <row r="379">
@@ -23586,13 +23586,13 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>157.68</v>
+        <v>158.21</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>5418-107-CM26</t>
+          <t>1422032-49-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -23612,17 +23612,17 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -23632,12 +23632,12 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K380" t="inlineStr"/>
@@ -23647,13 +23647,13 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>472.1</v>
+        <v>84.29000000000001</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>4062-382-CM26</t>
+          <t>4062-384-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -23708,13 +23708,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>434.5</v>
+        <v>401.91</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>4062-383-CM26</t>
+          <t>1208106-44-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -23739,12 +23739,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -23769,13 +23769,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>458.56</v>
+        <v>63.07</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1208106-47-CM26</t>
+          <t>1208106-45-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -23815,12 +23815,12 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K383" t="inlineStr"/>
@@ -23830,13 +23830,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>251.46</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>4062-384-CM26</t>
+          <t>1208106-46-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -23861,12 +23861,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -23876,12 +23876,12 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K384" t="inlineStr"/>
@@ -23891,13 +23891,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>400.63</v>
+        <v>392.79</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1208106-45-CM26</t>
+          <t>1208106-47-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -23937,12 +23937,12 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K385" t="inlineStr"/>
@@ -23952,13 +23952,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>97.89</v>
+        <v>252.26</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1208106-44-CM26</t>
+          <t>4062-382-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -23983,12 +23983,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -24013,13 +24013,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>62.86</v>
+        <v>435.88</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1208106-46-CM26</t>
+          <t>4062-383-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -24044,12 +24044,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -24059,12 +24059,12 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K387" t="inlineStr"/>
@@ -24074,13 +24074,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>391.54</v>
+        <v>460.02</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1875-14-CM26</t>
+          <t>5418-110-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -24105,12 +24105,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>60.704.000-1</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE TURISMO</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -24135,13 +24135,13 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>548.61</v>
+        <v>235.29</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>5418-110-CM26</t>
+          <t>1875-14-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -24166,12 +24166,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -24196,7 +24196,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>234.05</v>
+        <v>551.52</v>
       </c>
     </row>
     <row r="390">
@@ -24257,7 +24257,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>146.78</v>
+        <v>147.56</v>
       </c>
     </row>
     <row r="391">
@@ -24318,7 +24318,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>1550.74</v>
+        <v>1572.93</v>
       </c>
     </row>
     <row r="392">
@@ -24379,7 +24379,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>663.1900000000001</v>
+        <v>672.6799999999999</v>
       </c>
     </row>
     <row r="393">
@@ -24440,7 +24440,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>87.45999999999999</v>
+        <v>88.72</v>
       </c>
     </row>
     <row r="394">
@@ -24501,7 +24501,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>43.63</v>
+        <v>44.25</v>
       </c>
     </row>
     <row r="395">
@@ -24566,7 +24566,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>142.63</v>
+        <v>144.3</v>
       </c>
     </row>
     <row r="396">
@@ -24627,7 +24627,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>2279.8</v>
+        <v>2318.36</v>
       </c>
     </row>
     <row r="397">
@@ -24688,7 +24688,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>124.01</v>
+        <v>126.11</v>
       </c>
     </row>
     <row r="398">
@@ -24749,7 +24749,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>424.47</v>
+        <v>428.79</v>
       </c>
     </row>
     <row r="399">
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>212.24</v>
+        <v>214.39</v>
       </c>
     </row>
     <row r="400">
@@ -24871,7 +24871,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>160.77</v>
+        <v>162.41</v>
       </c>
     </row>
     <row r="401">
@@ -24932,7 +24932,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>184.69</v>
+        <v>186.56</v>
       </c>
     </row>
     <row r="402">
@@ -24993,7 +24993,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>187.67</v>
+        <v>189.58</v>
       </c>
     </row>
     <row r="403">
@@ -25054,7 +25054,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>152.13</v>
+        <v>153.67</v>
       </c>
     </row>
     <row r="404">
@@ -25115,7 +25115,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>134.79</v>
+        <v>136.16</v>
       </c>
     </row>
     <row r="405">
@@ -25176,13 +25176,13 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>157.42</v>
+        <v>158.89</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1057547-8426-CM26</t>
+          <t>5418-117-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -25207,12 +25207,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -25237,13 +25237,13 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>170.65</v>
+        <v>249.9</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>5418-117-CM26</t>
+          <t>926853-23-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -25268,12 +25268,12 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>Zona de Bienestar Valdivia</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -25283,12 +25283,12 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K407" t="inlineStr"/>
@@ -25298,13 +25298,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>247.58</v>
+        <v>265.97</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>926853-23-CM26</t>
+          <t>1057547-8426-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -25329,12 +25329,12 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -25344,12 +25344,12 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K408" t="inlineStr"/>
@@ -25359,13 +25359,13 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>263.5</v>
+        <v>172.25</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2281-747-CM26</t>
+          <t>2281-746-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -25420,13 +25420,13 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>65.04000000000001</v>
+        <v>1473.8</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2281-746-CM26</t>
+          <t>2281-747-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -25481,7 +25481,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>1460.11</v>
+        <v>65.65000000000001</v>
       </c>
     </row>
     <row r="411">
@@ -25542,13 +25542,13 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>813.37</v>
+        <v>821</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>5668-26-CM26</t>
+          <t>5650-20-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -25568,17 +25568,17 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.402.010-5</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Regional Min.Bs.Nac. XIV Región Los Rios</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -25603,13 +25603,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>278.45</v>
+        <v>102.62</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>5722-5-CM26</t>
+          <t>5650-19-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -25629,17 +25629,17 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.402.010-5</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Regional Min.Bs.Nac. XIV Región Los Rios</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -25649,12 +25649,12 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K413" t="inlineStr"/>
@@ -25664,13 +25664,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>100.53</v>
+        <v>140.97</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>5650-18-CM26</t>
+          <t>5650-21-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -25710,12 +25710,12 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K414" t="inlineStr"/>
@@ -25725,13 +25725,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>50.84</v>
+        <v>108.55</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>5650-19-CM26</t>
+          <t>5722-5-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -25751,17 +25751,17 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>61.402.010-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Regional Min.Bs.Nac. XIV Región Los Rios</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -25771,12 +25771,12 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K415" t="inlineStr"/>
@@ -25786,13 +25786,13 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>142.05</v>
+        <v>99.77</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>5650-20-CM26</t>
+          <t>5668-26-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -25812,17 +25812,17 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>61.402.010-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Regional Min.Bs.Nac. XIV Región Los Rios</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -25847,13 +25847,13 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>103.4</v>
+        <v>276.33</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>5650-21-CM26</t>
+          <t>5650-18-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -25893,12 +25893,12 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K417" t="inlineStr"/>
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>109.38</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="418">
@@ -25969,7 +25969,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>184.82</v>
+        <v>181.7</v>
       </c>
     </row>
     <row r="419">
@@ -26030,7 +26030,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>211.27</v>
+        <v>207.7</v>
       </c>
     </row>
     <row r="420">
@@ -26091,7 +26091,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>117.35</v>
+        <v>115.37</v>
       </c>
     </row>
     <row r="421">
@@ -26152,7 +26152,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>311.53</v>
+        <v>306.27</v>
       </c>
     </row>
     <row r="422">
@@ -26213,7 +26213,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>129.21</v>
+        <v>127.38</v>
       </c>
     </row>
     <row r="423">
@@ -26274,7 +26274,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>361.14</v>
+        <v>356.01</v>
       </c>
     </row>
     <row r="424">
@@ -26335,7 +26335,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>208.71</v>
+        <v>205.84</v>
       </c>
     </row>
     <row r="425">
@@ -26396,13 +26396,13 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>191.86</v>
+        <v>189.22</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>5742-47-CM26</t>
+          <t>5742-48-CM26</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -26457,7 +26457,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>122.24</v>
+        <v>125.54</v>
       </c>
     </row>
     <row r="427">
@@ -26518,13 +26518,13 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>254.13</v>
+        <v>252.56</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>5742-48-CM26</t>
+          <t>5742-47-CM26</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -26579,7 +26579,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>126.32</v>
+        <v>121.48</v>
       </c>
     </row>
     <row r="429">
@@ -26640,7 +26640,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>607.8099999999999</v>
+        <v>616.86</v>
       </c>
     </row>
     <row r="430">
@@ -26701,7 +26701,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>146.85</v>
+        <v>149.03</v>
       </c>
     </row>
     <row r="431">
@@ -26762,7 +26762,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>81.31999999999999</v>
+        <v>83.15000000000001</v>
       </c>
     </row>
     <row r="432">
@@ -26823,7 +26823,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>119.34</v>
+        <v>122.04</v>
       </c>
     </row>
     <row r="433">
@@ -26884,7 +26884,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>217.87</v>
+        <v>219.37</v>
       </c>
     </row>
     <row r="434">
@@ -26945,7 +26945,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>136.55</v>
+        <v>137.49</v>
       </c>
     </row>
     <row r="435">
@@ -27006,13 +27006,13 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>1581.01</v>
+        <v>1591.93</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>5418-133-CM26</t>
+          <t>912853-5-CM26</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -27032,17 +27032,17 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.980.570-4</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>Com.Desarrollo Productivo Regional de Los Ríos</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -27052,12 +27052,12 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K436" t="inlineStr"/>
@@ -27067,13 +27067,13 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>202.73</v>
+        <v>247.65</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>780724-64-CM26</t>
+          <t>2180-92-CM26</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -27093,17 +27093,17 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>61.980.330-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Ilustre Tercer Tribunal Ambiental</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -27113,12 +27113,12 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K437" t="inlineStr"/>
@@ -27128,13 +27128,13 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>81.86</v>
+        <v>165.38</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>780724-63-CM26</t>
+          <t>5418-131-CM26</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -27159,12 +27159,12 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>61.980.330-2</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Ilustre Tercer Tribunal Ambiental</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -27174,12 +27174,12 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K438" t="inlineStr"/>
@@ -27189,13 +27189,13 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>116.47</v>
+        <v>2410.64</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>5418-131-CM26</t>
+          <t>5418-132-CM26</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -27250,13 +27250,13 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>2403.21</v>
+        <v>301.33</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2180-92-CM26</t>
+          <t>5418-133-CM26</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -27276,17 +27276,17 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -27311,13 +27311,13 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>164.87</v>
+        <v>203.36</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>912853-5-CM26</t>
+          <t>780724-63-CM26</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -27337,17 +27337,17 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>61.980.570-4</t>
+          <t>61.980.330-2</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Com.Desarrollo Productivo Regional de Los Ríos</t>
+          <t>Ilustre Tercer Tribunal Ambiental</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -27357,12 +27357,12 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K441" t="inlineStr"/>
@@ -27372,13 +27372,13 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>246.88</v>
+        <v>116.83</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>5418-132-CM26</t>
+          <t>780724-64-CM26</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -27403,12 +27403,12 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.980.330-2</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>Ilustre Tercer Tribunal Ambiental</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -27433,13 +27433,13 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>300.4</v>
+        <v>82.12</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>5740-222-CM26</t>
+          <t>1057547-9476-CM26</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -27464,12 +27464,12 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -27494,13 +27494,13 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>288.41</v>
+        <v>161.75</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2180-95-CM26</t>
+          <t>5740-222-CM26</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -27520,17 +27520,17 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -27555,13 +27555,13 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>171.85</v>
+        <v>287.65</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>1057547-9476-CM26</t>
+          <t>2180-95-CM26</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -27581,17 +27581,17 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -27616,7 +27616,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>162.18</v>
+        <v>171.39</v>
       </c>
     </row>
     <row r="446">
@@ -27677,13 +27677,13 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>227.64</v>
+        <v>224.61</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>5418-140-CM26</t>
+          <t>5418-138-CM26</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -27738,13 +27738,13 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>253.45</v>
+        <v>263.06</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>5418-138-CM26</t>
+          <t>2180-100-CM26</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -27764,17 +27764,17 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -27784,12 +27784,12 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K448" t="inlineStr"/>
@@ -27799,13 +27799,13 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>268.31</v>
+        <v>270.07</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2180-100-CM26</t>
+          <t>5418-139-CM26</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -27825,17 +27825,17 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -27845,12 +27845,12 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K449" t="inlineStr"/>
@@ -27860,13 +27860,13 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>275.46</v>
+        <v>238.21</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>5418-139-CM26</t>
+          <t>5418-140-CM26</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -27921,13 +27921,13 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>242.97</v>
+        <v>248.49</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>1283719-92-CM26</t>
+          <t>1057547-9621-CM26</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -27952,12 +27952,12 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>72.738.600-9</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL DE LA ILUSTRE MUNICIPALIDAD DE VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -27982,13 +27982,13 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>392.66</v>
+        <v>193.93</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>1283719-93-CM26</t>
+          <t>1283719-90-CM26</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -28043,13 +28043,13 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>87.26000000000001</v>
+        <v>775.52</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>1057547-9621-CM26</t>
+          <t>1283719-91-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -28074,12 +28074,12 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>72.738.600-9</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>CORPORACION CULTURAL DE LA ILUSTRE MUNICIPALIDAD DE VALDIVIA</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -28104,13 +28104,13 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>196.85</v>
+        <v>201.78</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>1283719-90-CM26</t>
+          <t>1283719-92-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -28165,13 +28165,13 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>787.1799999999999</v>
+        <v>386.85</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>1283719-91-CM26</t>
+          <t>1283719-93-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -28226,13 +28226,13 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>204.82</v>
+        <v>85.97</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>1340-325-CM26</t>
+          <t>1422032-62-CM26</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -28252,17 +28252,17 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -28287,13 +28287,13 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>297.87</v>
+        <v>365.9</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>1422032-62-CM26</t>
+          <t>2281-850-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -28318,12 +28318,12 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -28333,12 +28333,12 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K457" t="inlineStr"/>
@@ -28348,13 +28348,13 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>373.58</v>
+        <v>205.07</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2281-850-CM26</t>
+          <t>1340-325-CM26</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -28374,17 +28374,17 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -28394,12 +28394,12 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K458" t="inlineStr"/>
@@ -28409,13 +28409,13 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>209.37</v>
+        <v>291.74</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>4777-523-CM26</t>
+          <t>5877-28-CM26</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -28435,17 +28435,17 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.979.170-3</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>Subsecretaria de las Culturas y las Artes Región de los Rios</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -28470,13 +28470,13 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>426.32</v>
+        <v>182</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>5877-28-CM26</t>
+          <t>4777-523-CM26</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -28496,17 +28496,17 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>61.979.170-3</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región de los Rios</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -28531,7 +28531,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>180.29</v>
+        <v>430.37</v>
       </c>
     </row>
     <row r="461">
@@ -28592,7 +28592,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>69.73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="462">
@@ -28653,7 +28653,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>112.94</v>
+        <v>114.08</v>
       </c>
     </row>
     <row r="463">
@@ -28714,7 +28714,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>319.78</v>
+        <v>323</v>
       </c>
     </row>
     <row r="464">
@@ -28775,7 +28775,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>157.38</v>
+        <v>158.96</v>
       </c>
     </row>
     <row r="465">
@@ -28836,7 +28836,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>178.64</v>
+        <v>180.42</v>
       </c>
     </row>
     <row r="466">
@@ -28897,7 +28897,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>504.79</v>
+        <v>507.36</v>
       </c>
     </row>
     <row r="467">
@@ -28958,7 +28958,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>72.31</v>
+        <v>72.59</v>
       </c>
     </row>
     <row r="468">
@@ -29019,7 +29019,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>155.15</v>
+        <v>154.37</v>
       </c>
     </row>
     <row r="469">
@@ -29080,7 +29080,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>163.95</v>
+        <v>163.11</v>
       </c>
     </row>
     <row r="470">
@@ -29141,7 +29141,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>599.86</v>
+        <v>601.14</v>
       </c>
     </row>
     <row r="471">
@@ -29202,7 +29202,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>192.3</v>
+        <v>193.55</v>
       </c>
     </row>
     <row r="472">
@@ -29263,7 +29263,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>837.17</v>
+        <v>839.09</v>
       </c>
     </row>
     <row r="473">
@@ -29324,7 +29324,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>227.99</v>
+        <v>228.51</v>
       </c>
     </row>
     <row r="474">
@@ -29385,13 +29385,13 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>213.37</v>
+        <v>213.86</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>5657-210-CM26</t>
+          <t>926853-50-CM26</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -29411,17 +29411,17 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Zona de Bienestar Valdivia</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K475" t="inlineStr"/>
@@ -29446,13 +29446,13 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>51.48</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>5657-211-CM26</t>
+          <t>926853-49-CM26</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -29472,17 +29472,17 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Zona de Bienestar Valdivia</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -29492,12 +29492,12 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K476" t="inlineStr"/>
@@ -29507,13 +29507,13 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>54.54</v>
+        <v>49.55</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>926853-49-CM26</t>
+          <t>5657-210-CM26</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -29533,17 +29533,17 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -29553,12 +29553,12 @@
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K477" t="inlineStr"/>
@@ -29568,13 +29568,13 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>49.22</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>926853-50-CM26</t>
+          <t>5657-211-CM26</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -29594,17 +29594,17 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -29614,12 +29614,12 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K478" t="inlineStr"/>
@@ -29629,7 +29629,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>64.69</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="479">
@@ -29690,7 +29690,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>881.02</v>
+        <v>887.1799999999999</v>
       </c>
     </row>
     <row r="480">
@@ -29751,7 +29751,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>76.29000000000001</v>
+        <v>76.05</v>
       </c>
     </row>
     <row r="481">
@@ -29812,7 +29812,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>79.19</v>
+        <v>78.94</v>
       </c>
     </row>
     <row r="482">
@@ -29873,7 +29873,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>363.36</v>
+        <v>362.21</v>
       </c>
     </row>
     <row r="483">
@@ -29934,13 +29934,13 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>332</v>
+        <v>330.95</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>1497-159-CM26</t>
+          <t>1340-395-CM26</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -29960,17 +29960,17 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -29995,13 +29995,13 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>127.33</v>
+        <v>180.14</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>1340-395-CM26</t>
+          <t>5877-41-CM26</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.979.170-3</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Subsecretaria de las Culturas y las Artes Región de los Rios</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -30056,13 +30056,13 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>180.5</v>
+        <v>720.55</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>5877-41-CM26</t>
+          <t>1497-159-CM26</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -30082,17 +30082,17 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>61.979.170-3</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región de los Rios</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -30117,7 +30117,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>722</v>
+        <v>127.07</v>
       </c>
     </row>
     <row r="487">
@@ -30178,7 +30178,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>129.84</v>
+        <v>129.08</v>
       </c>
     </row>
     <row r="488">
@@ -30239,7 +30239,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>168.05</v>
+        <v>167.08</v>
       </c>
     </row>
     <row r="489">
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>248.4</v>
+        <v>246.96</v>
       </c>
     </row>
     <row r="490">
@@ -30361,7 +30361,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>60.71</v>
+        <v>60.35</v>
       </c>
     </row>
     <row r="491">
@@ -30422,13 +30422,13 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>135.24</v>
+        <v>134.45</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>912853-11-CM26</t>
+          <t>5740-262-CM26</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -30448,17 +30448,17 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>61.980.570-4</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>Com.Desarrollo Productivo Regional de Los Ríos</t>
+          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -30468,12 +30468,12 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K492" t="inlineStr"/>
@@ -30483,13 +30483,13 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>107.99</v>
+        <v>272.98</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2180-114-CM26</t>
+          <t>2180-115-CM26</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -30544,13 +30544,13 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>135.18</v>
+        <v>209.93</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2180-115-CM26</t>
+          <t>2180-114-CM26</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -30605,13 +30605,13 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>213.37</v>
+        <v>133</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>5740-262-CM26</t>
+          <t>912853-11-CM26</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -30631,17 +30631,17 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>61.980.570-4</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>Com.Desarrollo Productivo Regional de Los Ríos</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -30651,12 +30651,12 @@
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K495" t="inlineStr"/>
@@ -30666,13 +30666,13 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>277.45</v>
+        <v>106.25</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>5418-171-CM26</t>
+          <t>5418-170-CM26</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -30727,13 +30727,13 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>760.62</v>
+        <v>374.21</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>5740-264-CM26</t>
+          <t>5418-171-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -30753,17 +30753,17 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -30773,12 +30773,12 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K497" t="inlineStr"/>
@@ -30788,13 +30788,13 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>152.58</v>
+        <v>748.4299999999999</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>5418-170-CM26</t>
+          <t>5740-264-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -30814,17 +30814,17 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -30834,12 +30834,12 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K498" t="inlineStr"/>
@@ -30849,7 +30849,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>380.31</v>
+        <v>150.14</v>
       </c>
     </row>
     <row r="499">
@@ -30910,7 +30910,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>115.73</v>
+        <v>114.38</v>
       </c>
     </row>
     <row r="500">
@@ -30971,7 +30971,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>126.56</v>
+        <v>125.09</v>
       </c>
     </row>
     <row r="501">
@@ -31032,7 +31032,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>106.01</v>
+        <v>104.78</v>
       </c>
     </row>
     <row r="502">
@@ -31093,7 +31093,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>184.37</v>
+        <v>182.22</v>
       </c>
     </row>
     <row r="503">
@@ -31154,7 +31154,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>127.45</v>
+        <v>125.96</v>
       </c>
     </row>
     <row r="504">
@@ -31215,7 +31215,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>151.29</v>
+        <v>149.53</v>
       </c>
     </row>
     <row r="505">
@@ -31276,7 +31276,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>285.59</v>
+        <v>282.27</v>
       </c>
     </row>
     <row r="506">
@@ -31337,13 +31337,13 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>62.76</v>
+        <v>62.41</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>3833-493-CM26</t>
+          <t>3833-494-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -31398,13 +31398,13 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>231.73</v>
+        <v>296.24</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>1340-419-CM26</t>
+          <t>1221-9-CM26</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -31429,12 +31429,12 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -31459,13 +31459,13 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>88.66</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>3833-494-CM26</t>
+          <t>3833-493-CM26</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -31520,13 +31520,13 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>297.89</v>
+        <v>230.44</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>1221-9-CM26</t>
+          <t>1340-419-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -31551,12 +31551,12 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -31581,13 +31581,13 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>51.16</v>
+        <v>88.17</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>3833-501-CM26</t>
+          <t>1057547-11503-CM26</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -31607,17 +31607,17 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -31627,12 +31627,12 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K511" t="inlineStr"/>
@@ -31642,13 +31642,13 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>155.43</v>
+        <v>226.87</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>1057547-11503-CM26</t>
+          <t>3833-501-CM26</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -31668,17 +31668,17 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -31688,12 +31688,12 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K512" t="inlineStr"/>
@@ -31703,7 +31703,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>227.99</v>
+        <v>154.66</v>
       </c>
     </row>
     <row r="513">
@@ -31764,7 +31764,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>94.84999999999999</v>
+        <v>94.39</v>
       </c>
     </row>
     <row r="514">
@@ -31825,7 +31825,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>95.63</v>
+        <v>95.16</v>
       </c>
     </row>
     <row r="515">
@@ -31886,7 +31886,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>137.72</v>
+        <v>137.04</v>
       </c>
     </row>
     <row r="516">
@@ -31947,7 +31947,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>92.61</v>
+        <v>92.15000000000001</v>
       </c>
     </row>
     <row r="517">
@@ -32008,13 +32008,13 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>194.72</v>
+        <v>193.76</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2281-1039-CM26</t>
+          <t>2281-1038-CM26</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -32069,13 +32069,13 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>118.85</v>
+        <v>254.7</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>1057547-11576-CM26</t>
+          <t>2281-1039-CM26</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -32100,12 +32100,12 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -32115,12 +32115,12 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K519" t="inlineStr"/>
@@ -32130,13 +32130,13 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>378.4</v>
+        <v>119.65</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2281-1038-CM26</t>
+          <t>1057547-11576-CM26</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -32161,12 +32161,12 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -32176,12 +32176,12 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K520" t="inlineStr"/>
@@ -32191,7 +32191,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>253.01</v>
+        <v>380.93</v>
       </c>
     </row>
     <row r="521">
@@ -32252,7 +32252,251 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>330.06</v>
+        <v>332.27</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>620039-13-CM26</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>61.533.000-0</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr"/>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M522" s="2" t="n">
+        <v>522.7</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2281-1074-CM26</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>69.200.100-1</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr"/>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M523" s="2" t="n">
+        <v>380.09</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>1305560-76-CM26</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M524" s="2" t="n">
+        <v>148.07</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>5795-75-CM26</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>61.979.130-4</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr"/>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M525" s="2" t="n">
+        <v>302.38</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/los-rios.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/los-rios.xlsx
@@ -89504,7 +89504,7 @@
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C1371" t="inlineStr">

--- a/docs/oc-regiones/pasajes-aereos-nacionales/los-rios.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1484"/>
+  <dimension ref="A1:M1486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -36394,7 +36394,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>5722-64-CM25</t>
+          <t>5418-207-CM25</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -36419,12 +36419,12 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -36434,12 +36434,12 @@
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K554" t="inlineStr">
@@ -36453,7 +36453,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>128.96</v>
+        <v>2554.13</v>
       </c>
     </row>
     <row r="555">
@@ -36849,7 +36849,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>5418-207-CM25</t>
+          <t>5722-64-CM25</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -36874,12 +36874,12 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -36889,12 +36889,12 @@
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K561" t="inlineStr">
@@ -36908,7 +36908,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>2554.13</v>
+        <v>128.96</v>
       </c>
     </row>
     <row r="562">
@@ -37759,7 +37759,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>1208106-62-CM25</t>
+          <t>5612-131-CM25</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -37784,12 +37784,12 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J575" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K575" t="inlineStr">
@@ -37818,13 +37818,13 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>182.6</v>
+        <v>654.24</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>5612-131-CM25</t>
+          <t>1208106-62-CM25</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -37849,12 +37849,12 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -37864,12 +37864,12 @@
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K576" t="inlineStr">
@@ -37883,7 +37883,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>654.24</v>
+        <v>182.6</v>
       </c>
     </row>
     <row r="577">
@@ -60964,7 +60964,7 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>5472-5-CM26</t>
+          <t>591376-5-CM26</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
@@ -60989,12 +60989,12 @@
       </c>
       <c r="F932" t="inlineStr">
         <is>
-          <t>61.978.950-4</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H932" t="inlineStr">
@@ -61023,7 +61023,7 @@
         </is>
       </c>
       <c r="M932" s="2" t="n">
-        <v>162.8</v>
+        <v>161.76</v>
       </c>
     </row>
     <row r="933">
@@ -61094,7 +61094,7 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>591376-5-CM26</t>
+          <t>5472-5-CM26</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
@@ -61119,12 +61119,12 @@
       </c>
       <c r="F934" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.978.950-4</t>
         </is>
       </c>
       <c r="G934" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
         </is>
       </c>
       <c r="H934" t="inlineStr">
@@ -61153,13 +61153,13 @@
         </is>
       </c>
       <c r="M934" s="2" t="n">
-        <v>161.76</v>
+        <v>162.8</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>1283719-4-CM26</t>
+          <t>591376-4-CM26</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -61184,12 +61184,12 @@
       </c>
       <c r="F935" t="inlineStr">
         <is>
-          <t>72.738.600-9</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL DE LA ILUSTRE MUNICIPALIDAD DE VALDIVIA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H935" t="inlineStr">
@@ -61199,12 +61199,12 @@
       </c>
       <c r="I935" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J935" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K935" t="inlineStr">
@@ -61218,13 +61218,13 @@
         </is>
       </c>
       <c r="M935" s="2" t="n">
-        <v>118.89</v>
+        <v>68.81999999999999</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>591376-4-CM26</t>
+          <t>1283719-4-CM26</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
@@ -61249,12 +61249,12 @@
       </c>
       <c r="F936" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>72.738.600-9</t>
         </is>
       </c>
       <c r="G936" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>CORPORACION CULTURAL DE LA ILUSTRE MUNICIPALIDAD DE VALDIVIA</t>
         </is>
       </c>
       <c r="H936" t="inlineStr">
@@ -61264,12 +61264,12 @@
       </c>
       <c r="I936" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J936" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K936" t="inlineStr">
@@ -61283,7 +61283,7 @@
         </is>
       </c>
       <c r="M936" s="2" t="n">
-        <v>68.81999999999999</v>
+        <v>118.89</v>
       </c>
     </row>
     <row r="937">
@@ -62199,7 +62199,7 @@
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>1057547-1863-CM26</t>
+          <t>5097-2-CM26</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
@@ -62224,12 +62224,12 @@
       </c>
       <c r="F951" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G951" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H951" t="inlineStr">
@@ -62258,13 +62258,13 @@
         </is>
       </c>
       <c r="M951" s="2" t="n">
-        <v>412.51</v>
+        <v>106.29</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>5097-2-CM26</t>
+          <t>1057547-1863-CM26</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
@@ -62289,12 +62289,12 @@
       </c>
       <c r="F952" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G952" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H952" t="inlineStr">
@@ -62323,7 +62323,7 @@
         </is>
       </c>
       <c r="M952" s="2" t="n">
-        <v>106.29</v>
+        <v>412.51</v>
       </c>
     </row>
     <row r="953">
@@ -62654,7 +62654,7 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>1057547-2526-CM26</t>
+          <t>5668-4-CM26</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
@@ -62674,17 +62674,17 @@
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F958" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G958" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H958" t="inlineStr">
@@ -62713,13 +62713,13 @@
         </is>
       </c>
       <c r="M958" s="2" t="n">
-        <v>441.72</v>
+        <v>344.02</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>5668-4-CM26</t>
+          <t>1057547-2526-CM26</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
@@ -62739,17 +62739,17 @@
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F959" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G959" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H959" t="inlineStr">
@@ -62778,7 +62778,7 @@
         </is>
       </c>
       <c r="M959" s="2" t="n">
-        <v>344.02</v>
+        <v>441.72</v>
       </c>
     </row>
     <row r="960">
@@ -62979,7 +62979,7 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>780724-13-CM26</t>
+          <t>780724-12-CM26</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
@@ -63019,12 +63019,12 @@
       </c>
       <c r="I963" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J963" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K963" t="inlineStr">
@@ -63038,13 +63038,13 @@
         </is>
       </c>
       <c r="M963" s="2" t="n">
-        <v>220.6</v>
+        <v>77.39</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>780724-12-CM26</t>
+          <t>5877-2-CM26</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
@@ -63064,17 +63064,17 @@
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t>61.980.330-2</t>
+          <t>61.979.170-3</t>
         </is>
       </c>
       <c r="G964" t="inlineStr">
         <is>
-          <t>ILUSTRE TERCER TRIBUNAL AMBIENTAL</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H964" t="inlineStr">
@@ -63084,12 +63084,12 @@
       </c>
       <c r="I964" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J964" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K964" t="inlineStr">
@@ -63103,13 +63103,13 @@
         </is>
       </c>
       <c r="M964" s="2" t="n">
-        <v>77.39</v>
+        <v>247</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>5877-2-CM26</t>
+          <t>1305560-21-CM26</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
@@ -63129,17 +63129,17 @@
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t>61.979.170-3</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H965" t="inlineStr">
@@ -63168,13 +63168,13 @@
         </is>
       </c>
       <c r="M965" s="2" t="n">
-        <v>247</v>
+        <v>198.28</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>1305560-21-CM26</t>
+          <t>780724-13-CM26</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
@@ -63199,12 +63199,12 @@
       </c>
       <c r="F966" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.980.330-2</t>
         </is>
       </c>
       <c r="G966" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>ILUSTRE TERCER TRIBUNAL AMBIENTAL</t>
         </is>
       </c>
       <c r="H966" t="inlineStr">
@@ -63233,7 +63233,7 @@
         </is>
       </c>
       <c r="M966" s="2" t="n">
-        <v>198.28</v>
+        <v>220.6</v>
       </c>
     </row>
     <row r="967">
@@ -63499,7 +63499,7 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>5740-55-CM26</t>
+          <t>1497-18-CM26</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
@@ -63524,12 +63524,12 @@
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G971" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H971" t="inlineStr">
@@ -63539,12 +63539,12 @@
       </c>
       <c r="I971" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J971" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K971" t="inlineStr">
@@ -63558,13 +63558,13 @@
         </is>
       </c>
       <c r="M971" s="2" t="n">
-        <v>315.27</v>
+        <v>170.37</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>1497-17-CM26</t>
+          <t>5740-55-CM26</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
@@ -63589,12 +63589,12 @@
       </c>
       <c r="F972" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G972" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H972" t="inlineStr">
@@ -63604,12 +63604,12 @@
       </c>
       <c r="I972" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J972" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K972" t="inlineStr">
@@ -63623,13 +63623,13 @@
         </is>
       </c>
       <c r="M972" s="2" t="n">
-        <v>242.65</v>
+        <v>315.27</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>1497-18-CM26</t>
+          <t>1497-17-CM26</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
@@ -63688,7 +63688,7 @@
         </is>
       </c>
       <c r="M973" s="2" t="n">
-        <v>170.37</v>
+        <v>242.65</v>
       </c>
     </row>
     <row r="974">
@@ -64019,7 +64019,7 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>1057547-3512-CM26</t>
+          <t>5740-64-CM26</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
@@ -64044,12 +64044,12 @@
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G979" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H979" t="inlineStr">
@@ -64059,12 +64059,12 @@
       </c>
       <c r="I979" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J979" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K979" t="inlineStr">
@@ -64078,13 +64078,13 @@
         </is>
       </c>
       <c r="M979" s="2" t="n">
-        <v>237.5</v>
+        <v>169.43</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>5740-64-CM26</t>
+          <t>5740-65-CM26</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
@@ -64143,13 +64143,13 @@
         </is>
       </c>
       <c r="M980" s="2" t="n">
-        <v>169.43</v>
+        <v>297.62</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>5740-65-CM26</t>
+          <t>1057547-3512-CM26</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
@@ -64174,12 +64174,12 @@
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G981" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H981" t="inlineStr">
@@ -64189,12 +64189,12 @@
       </c>
       <c r="I981" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J981" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K981" t="inlineStr">
@@ -64208,7 +64208,7 @@
         </is>
       </c>
       <c r="M981" s="2" t="n">
-        <v>297.62</v>
+        <v>237.5</v>
       </c>
     </row>
     <row r="982">
@@ -64344,7 +64344,7 @@
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>523524-8-CM26</t>
+          <t>1395865-52-CM26</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
@@ -64364,17 +64364,17 @@
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F984" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>65.189.089-6</t>
         </is>
       </c>
       <c r="G984" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H984" t="inlineStr">
@@ -64403,13 +64403,13 @@
         </is>
       </c>
       <c r="M984" s="2" t="n">
-        <v>77.33</v>
+        <v>440.03</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>523524-9-CM26</t>
+          <t>523524-8-CM26</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
@@ -64468,13 +64468,13 @@
         </is>
       </c>
       <c r="M985" s="2" t="n">
-        <v>98.66</v>
+        <v>77.33</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>1395865-52-CM26</t>
+          <t>523524-9-CM26</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
@@ -64494,17 +64494,17 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F986" t="inlineStr">
         <is>
-          <t>65.189.089-6</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G986" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN PATRIMONIAL CULTURAL DE LA REGION DE LOS RIOS</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H986" t="inlineStr">
@@ -64533,7 +64533,7 @@
         </is>
       </c>
       <c r="M986" s="2" t="n">
-        <v>440.03</v>
+        <v>98.66</v>
       </c>
     </row>
     <row r="987">
@@ -64669,7 +64669,7 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>2180-17-CM26</t>
+          <t>1035685-63-CM26</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
@@ -64694,12 +64694,12 @@
       </c>
       <c r="F989" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G989" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H989" t="inlineStr">
@@ -64709,12 +64709,12 @@
       </c>
       <c r="I989" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J989" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K989" t="inlineStr">
@@ -64728,7 +64728,7 @@
         </is>
       </c>
       <c r="M989" s="2" t="n">
-        <v>208.06</v>
+        <v>70.78</v>
       </c>
     </row>
     <row r="990">
@@ -64799,7 +64799,7 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>1035685-63-CM26</t>
+          <t>1057547-3770-CM26</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
@@ -64819,17 +64819,17 @@
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F991" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G991" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H991" t="inlineStr">
@@ -64839,12 +64839,12 @@
       </c>
       <c r="I991" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J991" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K991" t="inlineStr">
@@ -64858,13 +64858,13 @@
         </is>
       </c>
       <c r="M991" s="2" t="n">
-        <v>70.78</v>
+        <v>159.4</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>1057547-3770-CM26</t>
+          <t>2180-17-CM26</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
@@ -64884,17 +64884,17 @@
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F992" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G992" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H992" t="inlineStr">
@@ -64923,7 +64923,7 @@
         </is>
       </c>
       <c r="M992" s="2" t="n">
-        <v>159.4</v>
+        <v>208.06</v>
       </c>
     </row>
     <row r="993">
@@ -65189,7 +65189,7 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>5418-48-CM26</t>
+          <t>5418-49-CM26</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
@@ -65254,7 +65254,7 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>5418-49-CM26</t>
+          <t>5418-48-CM26</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
@@ -65319,7 +65319,7 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>5418-50-CM26</t>
+          <t>1035685-71-CM26</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
@@ -65344,12 +65344,12 @@
       </c>
       <c r="F999" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G999" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H999" t="inlineStr">
@@ -65378,13 +65378,13 @@
         </is>
       </c>
       <c r="M999" s="2" t="n">
-        <v>126.57</v>
+        <v>80.95</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>1035685-71-CM26</t>
+          <t>5418-50-CM26</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
@@ -65409,12 +65409,12 @@
       </c>
       <c r="F1000" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G1000" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1000" t="inlineStr">
@@ -65443,7 +65443,7 @@
         </is>
       </c>
       <c r="M1000" s="2" t="n">
-        <v>80.95</v>
+        <v>126.57</v>
       </c>
     </row>
     <row r="1001">
@@ -65514,7 +65514,7 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>5740-83-CM26</t>
+          <t>5740-84-CM26</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
@@ -65573,13 +65573,13 @@
         </is>
       </c>
       <c r="M1002" s="2" t="n">
-        <v>191.47</v>
+        <v>323.81</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>1057547-4228-CM26</t>
+          <t>5740-83-CM26</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
@@ -65604,12 +65604,12 @@
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G1003" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1003" t="inlineStr">
@@ -65638,13 +65638,13 @@
         </is>
       </c>
       <c r="M1003" s="2" t="n">
-        <v>462.96</v>
+        <v>191.47</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>5740-84-CM26</t>
+          <t>1057547-4228-CM26</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
@@ -65669,12 +65669,12 @@
       </c>
       <c r="F1004" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G1004" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H1004" t="inlineStr">
@@ -65703,7 +65703,7 @@
         </is>
       </c>
       <c r="M1004" s="2" t="n">
-        <v>323.81</v>
+        <v>462.96</v>
       </c>
     </row>
     <row r="1005">
@@ -66294,7 +66294,7 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>2180-29-CM26</t>
+          <t>2180-30-CM26</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
@@ -66353,13 +66353,13 @@
         </is>
       </c>
       <c r="M1014" s="2" t="n">
-        <v>218.13</v>
+        <v>159.68</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>2180-30-CM26</t>
+          <t>1057545-325-CM26</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
@@ -66379,17 +66379,17 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G1015" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H1015" t="inlineStr">
@@ -66399,12 +66399,12 @@
       </c>
       <c r="I1015" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1015" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1015" t="inlineStr">
@@ -66418,13 +66418,13 @@
         </is>
       </c>
       <c r="M1015" s="2" t="n">
-        <v>159.68</v>
+        <v>126.03</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>1057545-325-CM26</t>
+          <t>1057545-326-CM26</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
@@ -66483,13 +66483,13 @@
         </is>
       </c>
       <c r="M1016" s="2" t="n">
-        <v>126.03</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>1057545-326-CM26</t>
+          <t>2180-29-CM26</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -66509,17 +66509,17 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1017" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1017" t="inlineStr">
@@ -66529,12 +66529,12 @@
       </c>
       <c r="I1017" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1017" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1017" t="inlineStr">
@@ -66548,7 +66548,7 @@
         </is>
       </c>
       <c r="M1017" s="2" t="n">
-        <v>78.25</v>
+        <v>218.13</v>
       </c>
     </row>
     <row r="1018">
@@ -66619,7 +66619,7 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>2180-31-CM26</t>
+          <t>508994-12-CM26</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
@@ -66639,17 +66639,17 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.979.160-6</t>
         </is>
       </c>
       <c r="G1019" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H1019" t="inlineStr">
@@ -66678,13 +66678,13 @@
         </is>
       </c>
       <c r="M1019" s="2" t="n">
-        <v>212.51</v>
+        <v>321.58</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>1057545-331-CM26</t>
+          <t>1208106-26-CM26</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
@@ -66709,12 +66709,12 @@
       </c>
       <c r="F1020" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G1020" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H1020" t="inlineStr">
@@ -66724,12 +66724,12 @@
       </c>
       <c r="I1020" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1020" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1020" t="inlineStr">
@@ -66743,13 +66743,13 @@
         </is>
       </c>
       <c r="M1020" s="2" t="n">
-        <v>79.58</v>
+        <v>220.7</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>1208106-26-CM26</t>
+          <t>1057545-331-CM26</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -66774,12 +66774,12 @@
       </c>
       <c r="F1021" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G1021" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H1021" t="inlineStr">
@@ -66789,12 +66789,12 @@
       </c>
       <c r="I1021" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1021" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1021" t="inlineStr">
@@ -66808,13 +66808,13 @@
         </is>
       </c>
       <c r="M1021" s="2" t="n">
-        <v>220.7</v>
+        <v>79.58</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>508994-12-CM26</t>
+          <t>2180-31-CM26</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
@@ -66834,17 +66834,17 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
-          <t>61.979.160-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1022" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1022" t="inlineStr">
@@ -66873,7 +66873,7 @@
         </is>
       </c>
       <c r="M1022" s="2" t="n">
-        <v>321.58</v>
+        <v>212.51</v>
       </c>
     </row>
     <row r="1023">
@@ -67009,7 +67009,7 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>1208106-29-CM26</t>
+          <t>1208106-30-CM26</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -67068,13 +67068,13 @@
         </is>
       </c>
       <c r="M1025" s="2" t="n">
-        <v>150.4</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>1208106-30-CM26</t>
+          <t>1208106-29-CM26</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
@@ -67133,7 +67133,7 @@
         </is>
       </c>
       <c r="M1026" s="2" t="n">
-        <v>61.1</v>
+        <v>150.4</v>
       </c>
     </row>
     <row r="1027">
@@ -67204,7 +67204,7 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>1057547-5179-CM26</t>
+          <t>1491-34-CM26</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
@@ -67229,12 +67229,12 @@
       </c>
       <c r="F1028" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G1028" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H1028" t="inlineStr">
@@ -67263,13 +67263,13 @@
         </is>
       </c>
       <c r="M1028" s="2" t="n">
-        <v>233.8</v>
+        <v>202.69</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>1491-34-CM26</t>
+          <t>1057547-5179-CM26</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -67294,12 +67294,12 @@
       </c>
       <c r="F1029" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G1029" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H1029" t="inlineStr">
@@ -67328,7 +67328,7 @@
         </is>
       </c>
       <c r="M1029" s="2" t="n">
-        <v>202.69</v>
+        <v>233.8</v>
       </c>
     </row>
     <row r="1030">
@@ -67399,7 +67399,7 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>5740-107-CM26</t>
+          <t>2281-463-CM26</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -67424,12 +67424,12 @@
       </c>
       <c r="F1031" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G1031" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H1031" t="inlineStr">
@@ -67458,13 +67458,13 @@
         </is>
       </c>
       <c r="M1031" s="2" t="n">
-        <v>198.02</v>
+        <v>276.67</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>2281-466-CM26</t>
+          <t>2281-464-CM26</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
@@ -67523,13 +67523,13 @@
         </is>
       </c>
       <c r="M1032" s="2" t="n">
-        <v>188.31</v>
+        <v>372.94</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>2281-467-CM26</t>
+          <t>5740-107-CM26</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
@@ -67554,12 +67554,12 @@
       </c>
       <c r="F1033" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G1033" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1033" t="inlineStr">
@@ -67588,13 +67588,13 @@
         </is>
       </c>
       <c r="M1033" s="2" t="n">
-        <v>86.73</v>
+        <v>198.02</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>926853-5-CM26</t>
+          <t>2281-466-CM26</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
@@ -67619,12 +67619,12 @@
       </c>
       <c r="F1034" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G1034" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H1034" t="inlineStr">
@@ -67634,12 +67634,12 @@
       </c>
       <c r="I1034" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1034" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1034" t="inlineStr">
@@ -67653,13 +67653,13 @@
         </is>
       </c>
       <c r="M1034" s="2" t="n">
-        <v>388.6</v>
+        <v>188.31</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>2281-463-CM26</t>
+          <t>2281-467-CM26</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
@@ -67718,13 +67718,13 @@
         </is>
       </c>
       <c r="M1035" s="2" t="n">
-        <v>276.67</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>2281-464-CM26</t>
+          <t>926853-5-CM26</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
@@ -67749,12 +67749,12 @@
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G1036" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1036" t="inlineStr">
@@ -67764,12 +67764,12 @@
       </c>
       <c r="I1036" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1036" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1036" t="inlineStr">
@@ -67783,7 +67783,7 @@
         </is>
       </c>
       <c r="M1036" s="2" t="n">
-        <v>372.94</v>
+        <v>388.6</v>
       </c>
     </row>
     <row r="1037">
@@ -67919,7 +67919,7 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>3986-128-CM26</t>
+          <t>4777-313-CM26</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
@@ -67944,12 +67944,12 @@
       </c>
       <c r="F1039" t="inlineStr">
         <is>
-          <t>69.200.200-8</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G1039" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CORRAL</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H1039" t="inlineStr">
@@ -67978,13 +67978,13 @@
         </is>
       </c>
       <c r="M1039" s="2" t="n">
-        <v>328.31</v>
+        <v>200.45</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>4777-313-CM26</t>
+          <t>4777-314-CM26</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
@@ -68024,12 +68024,12 @@
       </c>
       <c r="I1040" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1040" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1040" t="inlineStr">
@@ -68043,13 +68043,13 @@
         </is>
       </c>
       <c r="M1040" s="2" t="n">
-        <v>200.45</v>
+        <v>142.99</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>4777-314-CM26</t>
+          <t>3986-127-CM26</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
@@ -68074,12 +68074,12 @@
       </c>
       <c r="F1041" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.200.200-8</t>
         </is>
       </c>
       <c r="G1041" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>MUNICIPALIDAD DE CORRAL</t>
         </is>
       </c>
       <c r="H1041" t="inlineStr">
@@ -68108,13 +68108,13 @@
         </is>
       </c>
       <c r="M1041" s="2" t="n">
-        <v>142.99</v>
+        <v>260.59</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>3986-127-CM26</t>
+          <t>3986-128-CM26</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
@@ -68154,12 +68154,12 @@
       </c>
       <c r="I1042" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1042" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1042" t="inlineStr">
@@ -68173,7 +68173,7 @@
         </is>
       </c>
       <c r="M1042" s="2" t="n">
-        <v>260.59</v>
+        <v>328.31</v>
       </c>
     </row>
     <row r="1043">
@@ -68244,7 +68244,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>5418-71-CM26</t>
+          <t>1173804-8-CM26</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
@@ -68269,12 +68269,12 @@
       </c>
       <c r="F1044" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G1044" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H1044" t="inlineStr">
@@ -68303,7 +68303,7 @@
         </is>
       </c>
       <c r="M1044" s="2" t="n">
-        <v>232.34</v>
+        <v>112.66</v>
       </c>
     </row>
     <row r="1045">
@@ -68439,7 +68439,7 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>5418-72-CM26</t>
+          <t>5418-71-CM26</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
@@ -68504,7 +68504,7 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>5418-73-CM26</t>
+          <t>5418-72-CM26</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
@@ -68569,7 +68569,7 @@
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>1173804-8-CM26</t>
+          <t>5418-73-CM26</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
@@ -68594,12 +68594,12 @@
       </c>
       <c r="F1049" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G1049" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1049" t="inlineStr">
@@ -68628,7 +68628,7 @@
         </is>
       </c>
       <c r="M1049" s="2" t="n">
-        <v>112.66</v>
+        <v>232.34</v>
       </c>
     </row>
     <row r="1050">
@@ -69089,7 +69089,7 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>5418-81-CM26</t>
+          <t>5668-13-CM26</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
@@ -69109,17 +69109,17 @@
       </c>
       <c r="E1057" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G1057" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H1057" t="inlineStr">
@@ -69129,12 +69129,12 @@
       </c>
       <c r="I1057" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1057" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1057" t="inlineStr">
@@ -69148,13 +69148,13 @@
         </is>
       </c>
       <c r="M1057" s="2" t="n">
-        <v>256.97</v>
+        <v>98.29000000000001</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>1057547-5670-CM26</t>
+          <t>5668-14-CM26</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
@@ -69174,17 +69174,17 @@
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G1058" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H1058" t="inlineStr">
@@ -69194,12 +69194,12 @@
       </c>
       <c r="I1058" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1058" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1058" t="inlineStr">
@@ -69213,13 +69213,13 @@
         </is>
       </c>
       <c r="M1058" s="2" t="n">
-        <v>471.21</v>
+        <v>109.68</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>5668-13-CM26</t>
+          <t>5418-80-CM26</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
@@ -69239,17 +69239,17 @@
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G1059" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1059" t="inlineStr">
@@ -69259,12 +69259,12 @@
       </c>
       <c r="I1059" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1059" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1059" t="inlineStr">
@@ -69278,13 +69278,13 @@
         </is>
       </c>
       <c r="M1059" s="2" t="n">
-        <v>98.29000000000001</v>
+        <v>493.34</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>5668-14-CM26</t>
+          <t>1057547-5670-CM26</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
@@ -69304,17 +69304,17 @@
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G1060" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H1060" t="inlineStr">
@@ -69324,12 +69324,12 @@
       </c>
       <c r="I1060" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1060" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1060" t="inlineStr">
@@ -69343,13 +69343,13 @@
         </is>
       </c>
       <c r="M1060" s="2" t="n">
-        <v>109.68</v>
+        <v>471.21</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>5418-80-CM26</t>
+          <t>5418-81-CM26</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
@@ -69408,7 +69408,7 @@
         </is>
       </c>
       <c r="M1061" s="2" t="n">
-        <v>493.34</v>
+        <v>256.97</v>
       </c>
     </row>
     <row r="1062">
@@ -69479,7 +69479,7 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>1340-187-CM26</t>
+          <t>5668-15-CM26</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
@@ -69538,13 +69538,13 @@
         </is>
       </c>
       <c r="M1063" s="2" t="n">
-        <v>125.31</v>
+        <v>252.77</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>780724-37-CM26</t>
+          <t>3986-136-CM26</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
@@ -69564,17 +69564,17 @@
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
-          <t>61.980.330-2</t>
+          <t>69.200.200-8</t>
         </is>
       </c>
       <c r="G1064" t="inlineStr">
         <is>
-          <t>ILUSTRE TERCER TRIBUNAL AMBIENTAL</t>
+          <t>MUNICIPALIDAD DE CORRAL</t>
         </is>
       </c>
       <c r="H1064" t="inlineStr">
@@ -69584,12 +69584,12 @@
       </c>
       <c r="I1064" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1064" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1064" t="inlineStr">
@@ -69603,13 +69603,13 @@
         </is>
       </c>
       <c r="M1064" s="2" t="n">
-        <v>122.47</v>
+        <v>581.15</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>3986-136-CM26</t>
+          <t>780724-37-CM26</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
@@ -69629,17 +69629,17 @@
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
-          <t>69.200.200-8</t>
+          <t>61.980.330-2</t>
         </is>
       </c>
       <c r="G1065" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CORRAL</t>
+          <t>ILUSTRE TERCER TRIBUNAL AMBIENTAL</t>
         </is>
       </c>
       <c r="H1065" t="inlineStr">
@@ -69649,12 +69649,12 @@
       </c>
       <c r="I1065" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1065" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1065" t="inlineStr">
@@ -69668,13 +69668,13 @@
         </is>
       </c>
       <c r="M1065" s="2" t="n">
-        <v>581.15</v>
+        <v>122.47</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>5668-15-CM26</t>
+          <t>1340-187-CM26</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
@@ -69733,7 +69733,7 @@
         </is>
       </c>
       <c r="M1066" s="2" t="n">
-        <v>252.77</v>
+        <v>125.31</v>
       </c>
     </row>
     <row r="1067">
@@ -69869,7 +69869,7 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>5740-120-CM26</t>
+          <t>2180-48-CM26</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
@@ -69889,17 +69889,17 @@
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1069" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1069" t="inlineStr">
@@ -69909,12 +69909,12 @@
       </c>
       <c r="I1069" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1069" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1069" t="inlineStr">
@@ -69928,7 +69928,7 @@
         </is>
       </c>
       <c r="M1069" s="2" t="n">
-        <v>590.11</v>
+        <v>482.72</v>
       </c>
     </row>
     <row r="1070">
@@ -69999,7 +69999,7 @@
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>2180-48-CM26</t>
+          <t>5740-121-CM26</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
@@ -70019,17 +70019,17 @@
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G1071" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1071" t="inlineStr">
@@ -70039,12 +70039,12 @@
       </c>
       <c r="I1071" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1071" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1071" t="inlineStr">
@@ -70058,13 +70058,13 @@
         </is>
       </c>
       <c r="M1071" s="2" t="n">
-        <v>482.72</v>
+        <v>197.42</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>523524-14-CM26</t>
+          <t>2180-47-CM26</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
@@ -70084,17 +70084,17 @@
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1072" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1072" t="inlineStr">
@@ -70123,13 +70123,13 @@
         </is>
       </c>
       <c r="M1072" s="2" t="n">
-        <v>247.41</v>
+        <v>297.8</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>2180-47-CM26</t>
+          <t>523524-14-CM26</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
@@ -70149,17 +70149,17 @@
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G1073" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H1073" t="inlineStr">
@@ -70188,13 +70188,13 @@
         </is>
       </c>
       <c r="M1073" s="2" t="n">
-        <v>297.8</v>
+        <v>247.41</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>5740-121-CM26</t>
+          <t>5740-120-CM26</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
@@ -70253,7 +70253,7 @@
         </is>
       </c>
       <c r="M1074" s="2" t="n">
-        <v>197.42</v>
+        <v>590.11</v>
       </c>
     </row>
     <row r="1075">
@@ -70454,12 +70454,12 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>5418-91-SE26</t>
+          <t>3833-309-CM26</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
@@ -70479,12 +70479,12 @@
       </c>
       <c r="F1078" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G1078" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H1078" t="inlineStr">
@@ -70513,18 +70513,18 @@
         </is>
       </c>
       <c r="M1078" s="2" t="n">
-        <v>45.68</v>
+        <v>502.66</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>3833-309-CM26</t>
+          <t>5418-91-SE26</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
@@ -70544,12 +70544,12 @@
       </c>
       <c r="F1079" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G1079" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1079" t="inlineStr">
@@ -70578,7 +70578,7 @@
         </is>
       </c>
       <c r="M1079" s="2" t="n">
-        <v>502.66</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="1080">
@@ -70714,7 +70714,7 @@
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>926853-15-CM26</t>
+          <t>3986-154-CM26</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
@@ -70734,17 +70734,17 @@
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>69.200.200-8</t>
         </is>
       </c>
       <c r="G1082" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MUNICIPALIDAD DE CORRAL</t>
         </is>
       </c>
       <c r="H1082" t="inlineStr">
@@ -70754,12 +70754,12 @@
       </c>
       <c r="I1082" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1082" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1082" t="inlineStr">
@@ -70773,13 +70773,13 @@
         </is>
       </c>
       <c r="M1082" s="2" t="n">
-        <v>122.46</v>
+        <v>199.84</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>5617-8-CM26</t>
+          <t>3986-155-CM26</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
@@ -70804,12 +70804,12 @@
       </c>
       <c r="F1083" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.200.200-8</t>
         </is>
       </c>
       <c r="G1083" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MUNICIPALIDAD DE CORRAL</t>
         </is>
       </c>
       <c r="H1083" t="inlineStr">
@@ -70838,13 +70838,13 @@
         </is>
       </c>
       <c r="M1083" s="2" t="n">
-        <v>386.68</v>
+        <v>199.84</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>3986-155-CM26</t>
+          <t>5617-8-CM26</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
@@ -70869,12 +70869,12 @@
       </c>
       <c r="F1084" t="inlineStr">
         <is>
-          <t>69.200.200-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G1084" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CORRAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H1084" t="inlineStr">
@@ -70903,7 +70903,7 @@
         </is>
       </c>
       <c r="M1084" s="2" t="n">
-        <v>199.84</v>
+        <v>386.68</v>
       </c>
     </row>
     <row r="1085">
@@ -70974,7 +70974,7 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>3986-154-CM26</t>
+          <t>926853-15-CM26</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
@@ -70994,17 +70994,17 @@
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
-          <t>69.200.200-8</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G1086" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CORRAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1086" t="inlineStr">
@@ -71014,12 +71014,12 @@
       </c>
       <c r="I1086" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1086" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1086" t="inlineStr">
@@ -71033,7 +71033,7 @@
         </is>
       </c>
       <c r="M1086" s="2" t="n">
-        <v>199.84</v>
+        <v>122.46</v>
       </c>
     </row>
     <row r="1087">
@@ -71169,7 +71169,7 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>1035685-142-CM26</t>
+          <t>1057545-479-CM26</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
@@ -71189,17 +71189,17 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G1089" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H1089" t="inlineStr">
@@ -71228,13 +71228,13 @@
         </is>
       </c>
       <c r="M1089" s="2" t="n">
-        <v>126.74</v>
+        <v>170.68</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>1057545-479-CM26</t>
+          <t>1035685-142-CM26</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
@@ -71254,17 +71254,17 @@
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G1090" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1090" t="inlineStr">
@@ -71293,13 +71293,13 @@
         </is>
       </c>
       <c r="M1090" s="2" t="n">
-        <v>170.68</v>
+        <v>126.74</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>1340-213-CM26</t>
+          <t>1422032-30-CM26</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
@@ -71324,12 +71324,12 @@
       </c>
       <c r="F1091" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G1091" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1091" t="inlineStr">
@@ -71358,13 +71358,13 @@
         </is>
       </c>
       <c r="M1091" s="2" t="n">
-        <v>154.73</v>
+        <v>95.55</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>1422032-30-CM26</t>
+          <t>1340-213-CM26</t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
@@ -71389,12 +71389,12 @@
       </c>
       <c r="F1092" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G1092" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H1092" t="inlineStr">
@@ -71423,7 +71423,7 @@
         </is>
       </c>
       <c r="M1092" s="2" t="n">
-        <v>95.55</v>
+        <v>154.73</v>
       </c>
     </row>
     <row r="1093">
@@ -71494,7 +71494,7 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>3762-372-CM26</t>
+          <t>1422032-32-CM26</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
@@ -71514,17 +71514,17 @@
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G1094" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1094" t="inlineStr">
@@ -71534,12 +71534,12 @@
       </c>
       <c r="I1094" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1094" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1094" t="inlineStr">
@@ -71553,13 +71553,13 @@
         </is>
       </c>
       <c r="M1094" s="2" t="n">
-        <v>78.48999999999999</v>
+        <v>260.04</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>1422032-32-CM26</t>
+          <t>3762-372-CM26</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
@@ -71579,17 +71579,17 @@
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G1095" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H1095" t="inlineStr">
@@ -71599,12 +71599,12 @@
       </c>
       <c r="I1095" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1095" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1095" t="inlineStr">
@@ -71618,13 +71618,13 @@
         </is>
       </c>
       <c r="M1095" s="2" t="n">
-        <v>260.04</v>
+        <v>78.48999999999999</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>2281-632-CM26</t>
+          <t>780724-50-CM26</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
@@ -71649,12 +71649,12 @@
       </c>
       <c r="F1096" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.980.330-2</t>
         </is>
       </c>
       <c r="G1096" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>ILUSTRE TERCER TRIBUNAL AMBIENTAL</t>
         </is>
       </c>
       <c r="H1096" t="inlineStr">
@@ -71664,12 +71664,12 @@
       </c>
       <c r="I1096" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1096" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1096" t="inlineStr">
@@ -71683,13 +71683,13 @@
         </is>
       </c>
       <c r="M1096" s="2" t="n">
-        <v>159.02</v>
+        <v>276.68</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>780724-51-CM26</t>
+          <t>5740-156-CM26</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
@@ -71714,12 +71714,12 @@
       </c>
       <c r="F1097" t="inlineStr">
         <is>
-          <t>61.980.330-2</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G1097" t="inlineStr">
         <is>
-          <t>ILUSTRE TERCER TRIBUNAL AMBIENTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1097" t="inlineStr">
@@ -71748,13 +71748,13 @@
         </is>
       </c>
       <c r="M1097" s="2" t="n">
-        <v>230.48</v>
+        <v>118.46</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>5740-156-CM26</t>
+          <t>2281-632-CM26</t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
@@ -71779,12 +71779,12 @@
       </c>
       <c r="F1098" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G1098" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H1098" t="inlineStr">
@@ -71794,12 +71794,12 @@
       </c>
       <c r="I1098" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1098" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1098" t="inlineStr">
@@ -71813,13 +71813,13 @@
         </is>
       </c>
       <c r="M1098" s="2" t="n">
-        <v>118.46</v>
+        <v>159.02</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>780724-50-CM26</t>
+          <t>780724-51-CM26</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
@@ -71878,13 +71878,13 @@
         </is>
       </c>
       <c r="M1099" s="2" t="n">
-        <v>276.68</v>
+        <v>230.48</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>5456-28-CM26</t>
+          <t>1422032-35-CM26</t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
@@ -71909,12 +71909,12 @@
       </c>
       <c r="F1100" t="inlineStr">
         <is>
-          <t>65.852.930-7</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G1100" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1100" t="inlineStr">
@@ -71943,13 +71943,13 @@
         </is>
       </c>
       <c r="M1100" s="2" t="n">
-        <v>87.12</v>
+        <v>115.71</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>1305560-51-CM26</t>
+          <t>1422032-36-CM26</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
@@ -71974,12 +71974,12 @@
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G1101" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1101" t="inlineStr">
@@ -72008,13 +72008,13 @@
         </is>
       </c>
       <c r="M1101" s="2" t="n">
-        <v>144.71</v>
+        <v>567.04</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>1422032-36-CM26</t>
+          <t>5456-27-CM26</t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
@@ -72034,17 +72034,17 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>65.852.930-7</t>
         </is>
       </c>
       <c r="G1102" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
         </is>
       </c>
       <c r="H1102" t="inlineStr">
@@ -72054,12 +72054,12 @@
       </c>
       <c r="I1102" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1102" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1102" t="inlineStr">
@@ -72073,13 +72073,13 @@
         </is>
       </c>
       <c r="M1102" s="2" t="n">
-        <v>567.04</v>
+        <v>275.37</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>1422032-35-CM26</t>
+          <t>5456-28-CM26</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
@@ -72104,12 +72104,12 @@
       </c>
       <c r="F1103" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>65.852.930-7</t>
         </is>
       </c>
       <c r="G1103" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
         </is>
       </c>
       <c r="H1103" t="inlineStr">
@@ -72138,13 +72138,13 @@
         </is>
       </c>
       <c r="M1103" s="2" t="n">
-        <v>115.71</v>
+        <v>87.12</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>5456-27-CM26</t>
+          <t>1305560-51-CM26</t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
@@ -72164,17 +72164,17 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
-          <t>65.852.930-7</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G1104" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H1104" t="inlineStr">
@@ -72184,12 +72184,12 @@
       </c>
       <c r="I1104" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1104" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1104" t="inlineStr">
@@ -72203,7 +72203,7 @@
         </is>
       </c>
       <c r="M1104" s="2" t="n">
-        <v>275.37</v>
+        <v>144.71</v>
       </c>
     </row>
     <row r="1105">
@@ -72404,7 +72404,7 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>1035685-154-CM26</t>
+          <t>1057547-7342-CM26</t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
@@ -72429,12 +72429,12 @@
       </c>
       <c r="F1108" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G1108" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H1108" t="inlineStr">
@@ -72463,13 +72463,13 @@
         </is>
       </c>
       <c r="M1108" s="2" t="n">
-        <v>121.8</v>
+        <v>407.96</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>1035685-155-CM26</t>
+          <t>591376-40-CM26</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
@@ -72494,12 +72494,12 @@
       </c>
       <c r="F1109" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G1109" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H1109" t="inlineStr">
@@ -72528,7 +72528,7 @@
         </is>
       </c>
       <c r="M1109" s="2" t="n">
-        <v>185.42</v>
+        <v>81.19</v>
       </c>
     </row>
     <row r="1110">
@@ -72599,7 +72599,7 @@
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>591376-40-CM26</t>
+          <t>1035685-155-CM26</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
@@ -72624,12 +72624,12 @@
       </c>
       <c r="F1111" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G1111" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1111" t="inlineStr">
@@ -72658,13 +72658,13 @@
         </is>
       </c>
       <c r="M1111" s="2" t="n">
-        <v>81.19</v>
+        <v>185.42</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>1057547-7342-CM26</t>
+          <t>1035685-154-CM26</t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
@@ -72689,12 +72689,12 @@
       </c>
       <c r="F1112" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G1112" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1112" t="inlineStr">
@@ -72723,7 +72723,7 @@
         </is>
       </c>
       <c r="M1112" s="2" t="n">
-        <v>407.96</v>
+        <v>121.8</v>
       </c>
     </row>
     <row r="1113">
@@ -72859,7 +72859,7 @@
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>5418-101-CM26</t>
+          <t>1875-13-CM26</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
@@ -72884,12 +72884,12 @@
       </c>
       <c r="F1115" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G1115" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H1115" t="inlineStr">
@@ -72918,13 +72918,13 @@
         </is>
       </c>
       <c r="M1115" s="2" t="n">
-        <v>1623.72</v>
+        <v>557.26</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>1875-13-CM26</t>
+          <t>1035685-162-CM26</t>
         </is>
       </c>
       <c r="B1116" t="inlineStr">
@@ -72949,12 +72949,12 @@
       </c>
       <c r="F1116" t="inlineStr">
         <is>
-          <t>60.704.000-1</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G1116" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE TURISMO</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1116" t="inlineStr">
@@ -72964,12 +72964,12 @@
       </c>
       <c r="I1116" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1116" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1116" t="inlineStr">
@@ -72983,7 +72983,7 @@
         </is>
       </c>
       <c r="M1116" s="2" t="n">
-        <v>557.26</v>
+        <v>86.97</v>
       </c>
     </row>
     <row r="1117">
@@ -73379,7 +73379,7 @@
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>1035685-162-CM26</t>
+          <t>5418-101-CM26</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
@@ -73404,12 +73404,12 @@
       </c>
       <c r="F1123" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G1123" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1123" t="inlineStr">
@@ -73419,12 +73419,12 @@
       </c>
       <c r="I1123" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1123" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1123" t="inlineStr">
@@ -73438,7 +73438,7 @@
         </is>
       </c>
       <c r="M1123" s="2" t="n">
-        <v>86.97</v>
+        <v>1623.72</v>
       </c>
     </row>
     <row r="1124">
@@ -73834,7 +73834,7 @@
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>1035685-167-CM26</t>
+          <t>1035685-166-CM26</t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
@@ -73893,13 +73893,13 @@
         </is>
       </c>
       <c r="M1130" s="2" t="n">
-        <v>110.62</v>
+        <v>126.35</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>1035685-166-CM26</t>
+          <t>2281-713-CM26</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
@@ -73919,17 +73919,17 @@
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1131" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G1131" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H1131" t="inlineStr">
@@ -73939,12 +73939,12 @@
       </c>
       <c r="I1131" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1131" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1131" t="inlineStr">
@@ -73958,13 +73958,13 @@
         </is>
       </c>
       <c r="M1131" s="2" t="n">
-        <v>126.35</v>
+        <v>237.9</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>2281-713-CM26</t>
+          <t>2281-712-CM26</t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
@@ -74023,13 +74023,13 @@
         </is>
       </c>
       <c r="M1132" s="2" t="n">
-        <v>237.9</v>
+        <v>307.77</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>2281-712-CM26</t>
+          <t>5650-15-CM26</t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
@@ -74049,17 +74049,17 @@
       </c>
       <c r="E1133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1133" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.402.010-5</t>
         </is>
       </c>
       <c r="G1133" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H1133" t="inlineStr">
@@ -74088,13 +74088,13 @@
         </is>
       </c>
       <c r="M1133" s="2" t="n">
-        <v>307.77</v>
+        <v>141.41</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>5650-15-CM26</t>
+          <t>1035685-167-CM26</t>
         </is>
       </c>
       <c r="B1134" t="inlineStr">
@@ -74119,12 +74119,12 @@
       </c>
       <c r="F1134" t="inlineStr">
         <is>
-          <t>61.402.010-5</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G1134" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1134" t="inlineStr">
@@ -74134,12 +74134,12 @@
       </c>
       <c r="I1134" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1134" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1134" t="inlineStr">
@@ -74153,13 +74153,13 @@
         </is>
       </c>
       <c r="M1134" s="2" t="n">
-        <v>141.41</v>
+        <v>110.62</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>1340-267-CM26</t>
+          <t>2905-359-CM26</t>
         </is>
       </c>
       <c r="B1135" t="inlineStr">
@@ -74179,17 +74179,17 @@
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1135" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G1135" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H1135" t="inlineStr">
@@ -74218,13 +74218,13 @@
         </is>
       </c>
       <c r="M1135" s="2" t="n">
-        <v>242.4</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>2905-363-CM26</t>
+          <t>1340-267-CM26</t>
         </is>
       </c>
       <c r="B1136" t="inlineStr">
@@ -74244,17 +74244,17 @@
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1136" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G1136" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H1136" t="inlineStr">
@@ -74283,13 +74283,13 @@
         </is>
       </c>
       <c r="M1136" s="2" t="n">
-        <v>479.83</v>
+        <v>242.4</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>2905-361-CM26</t>
+          <t>2905-363-CM26</t>
         </is>
       </c>
       <c r="B1137" t="inlineStr">
@@ -74348,13 +74348,13 @@
         </is>
       </c>
       <c r="M1137" s="2" t="n">
-        <v>182.28</v>
+        <v>479.83</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>2905-359-CM26</t>
+          <t>2905-362-CM26</t>
         </is>
       </c>
       <c r="B1138" t="inlineStr">
@@ -74413,13 +74413,13 @@
         </is>
       </c>
       <c r="M1138" s="2" t="n">
-        <v>143</v>
+        <v>476.53</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>3762-432-CM26</t>
+          <t>2905-360-CM26</t>
         </is>
       </c>
       <c r="B1139" t="inlineStr">
@@ -74439,17 +74439,17 @@
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1139" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G1139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H1139" t="inlineStr">
@@ -74478,13 +74478,13 @@
         </is>
       </c>
       <c r="M1139" s="2" t="n">
-        <v>198.97</v>
+        <v>67.25</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>5418-107-CM26</t>
+          <t>3762-432-CM26</t>
         </is>
       </c>
       <c r="B1140" t="inlineStr">
@@ -74504,17 +74504,17 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1140" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G1140" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H1140" t="inlineStr">
@@ -74543,13 +74543,13 @@
         </is>
       </c>
       <c r="M1140" s="2" t="n">
-        <v>473.67</v>
+        <v>198.97</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>2905-362-CM26</t>
+          <t>2905-361-CM26</t>
         </is>
       </c>
       <c r="B1141" t="inlineStr">
@@ -74608,7 +74608,7 @@
         </is>
       </c>
       <c r="M1141" s="2" t="n">
-        <v>476.53</v>
+        <v>182.28</v>
       </c>
     </row>
     <row r="1142">
@@ -74874,7 +74874,7 @@
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>2905-360-CM26</t>
+          <t>5418-107-CM26</t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
@@ -74899,12 +74899,12 @@
       </c>
       <c r="F1146" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G1146" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1146" t="inlineStr">
@@ -74933,7 +74933,7 @@
         </is>
       </c>
       <c r="M1146" s="2" t="n">
-        <v>67.25</v>
+        <v>473.67</v>
       </c>
     </row>
     <row r="1147">
@@ -76499,7 +76499,7 @@
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>1723-291-CM26</t>
+          <t>1723-292-CM26</t>
         </is>
       </c>
       <c r="B1171" t="inlineStr">
@@ -76539,12 +76539,12 @@
       </c>
       <c r="I1171" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1171" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1171" t="inlineStr">
@@ -76558,13 +76558,13 @@
         </is>
       </c>
       <c r="M1171" s="2" t="n">
-        <v>189.58</v>
+        <v>153.67</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>1723-292-CM26</t>
+          <t>1723-293-CM26</t>
         </is>
       </c>
       <c r="B1172" t="inlineStr">
@@ -76604,12 +76604,12 @@
       </c>
       <c r="I1172" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J1172" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K1172" t="inlineStr">
@@ -76623,13 +76623,13 @@
         </is>
       </c>
       <c r="M1172" s="2" t="n">
-        <v>153.67</v>
+        <v>136.16</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>1723-293-CM26</t>
+          <t>1723-291-CM26</t>
         </is>
       </c>
       <c r="B1173" t="inlineStr">
@@ -76669,12 +76669,12 @@
       </c>
       <c r="I1173" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1173" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1173" t="inlineStr">
@@ -76688,13 +76688,13 @@
         </is>
       </c>
       <c r="M1173" s="2" t="n">
-        <v>136.16</v>
+        <v>189.58</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>2281-747-CM26</t>
+          <t>5612-95-CM26</t>
         </is>
       </c>
       <c r="B1174" t="inlineStr">
@@ -76719,12 +76719,12 @@
       </c>
       <c r="F1174" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G1174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H1174" t="inlineStr">
@@ -76734,12 +76734,12 @@
       </c>
       <c r="I1174" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1174" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1174" t="inlineStr">
@@ -76753,13 +76753,13 @@
         </is>
       </c>
       <c r="M1174" s="2" t="n">
-        <v>65.65000000000001</v>
+        <v>158.89</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>926853-23-CM26</t>
+          <t>1057547-8426-CM26</t>
         </is>
       </c>
       <c r="B1175" t="inlineStr">
@@ -76784,12 +76784,12 @@
       </c>
       <c r="F1175" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G1175" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H1175" t="inlineStr">
@@ -76799,12 +76799,12 @@
       </c>
       <c r="I1175" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1175" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1175" t="inlineStr">
@@ -76818,7 +76818,7 @@
         </is>
       </c>
       <c r="M1175" s="2" t="n">
-        <v>265.97</v>
+        <v>172.25</v>
       </c>
     </row>
     <row r="1176">
@@ -76889,7 +76889,7 @@
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>1057547-8426-CM26</t>
+          <t>926853-23-CM26</t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
@@ -76914,12 +76914,12 @@
       </c>
       <c r="F1177" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G1177" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1177" t="inlineStr">
@@ -76929,12 +76929,12 @@
       </c>
       <c r="I1177" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1177" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1177" t="inlineStr">
@@ -76948,13 +76948,13 @@
         </is>
       </c>
       <c r="M1177" s="2" t="n">
-        <v>172.25</v>
+        <v>265.97</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>5612-95-CM26</t>
+          <t>2281-747-CM26</t>
         </is>
       </c>
       <c r="B1178" t="inlineStr">
@@ -76979,12 +76979,12 @@
       </c>
       <c r="F1178" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G1178" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H1178" t="inlineStr">
@@ -76994,12 +76994,12 @@
       </c>
       <c r="I1178" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1178" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1178" t="inlineStr">
@@ -77013,7 +77013,7 @@
         </is>
       </c>
       <c r="M1178" s="2" t="n">
-        <v>158.89</v>
+        <v>65.65000000000001</v>
       </c>
     </row>
     <row r="1179">
@@ -77279,7 +77279,7 @@
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>5650-18-CM26</t>
+          <t>5650-19-CM26</t>
         </is>
       </c>
       <c r="B1183" t="inlineStr">
@@ -77338,13 +77338,13 @@
         </is>
       </c>
       <c r="M1183" s="2" t="n">
-        <v>50.46</v>
+        <v>140.97</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>5722-5-CM26</t>
+          <t>5650-18-CM26</t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
@@ -77364,17 +77364,17 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1184" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.402.010-5</t>
         </is>
       </c>
       <c r="G1184" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H1184" t="inlineStr">
@@ -77384,12 +77384,12 @@
       </c>
       <c r="I1184" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1184" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1184" t="inlineStr">
@@ -77403,13 +77403,13 @@
         </is>
       </c>
       <c r="M1184" s="2" t="n">
-        <v>99.77</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>5668-26-CM26</t>
+          <t>5722-5-CM26</t>
         </is>
       </c>
       <c r="B1185" t="inlineStr">
@@ -77468,13 +77468,13 @@
         </is>
       </c>
       <c r="M1185" s="2" t="n">
-        <v>276.33</v>
+        <v>99.77</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>5650-19-CM26</t>
+          <t>5668-26-CM26</t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
@@ -77494,17 +77494,17 @@
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1186" t="inlineStr">
         <is>
-          <t>61.402.010-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G1186" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H1186" t="inlineStr">
@@ -77514,12 +77514,12 @@
       </c>
       <c r="I1186" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1186" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1186" t="inlineStr">
@@ -77533,13 +77533,13 @@
         </is>
       </c>
       <c r="M1186" s="2" t="n">
-        <v>140.97</v>
+        <v>276.33</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>1271-14-CM26</t>
+          <t>5418-122-CM26</t>
         </is>
       </c>
       <c r="B1187" t="inlineStr">
@@ -77559,17 +77559,17 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1187" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G1187" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1187" t="inlineStr">
@@ -77598,13 +77598,13 @@
         </is>
       </c>
       <c r="M1187" s="2" t="n">
-        <v>181.7</v>
+        <v>207.7</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>5722-6-CM26</t>
+          <t>1057545-621-CM26</t>
         </is>
       </c>
       <c r="B1188" t="inlineStr">
@@ -77624,17 +77624,17 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1188" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G1188" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H1188" t="inlineStr">
@@ -77663,13 +77663,13 @@
         </is>
       </c>
       <c r="M1188" s="2" t="n">
-        <v>115.37</v>
+        <v>306.27</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>1057545-621-CM26</t>
+          <t>1271-14-CM26</t>
         </is>
       </c>
       <c r="B1189" t="inlineStr">
@@ -77689,17 +77689,17 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1189" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G1189" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H1189" t="inlineStr">
@@ -77709,12 +77709,12 @@
       </c>
       <c r="I1189" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1189" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1189" t="inlineStr">
@@ -77728,13 +77728,13 @@
         </is>
       </c>
       <c r="M1189" s="2" t="n">
-        <v>306.27</v>
+        <v>181.7</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>5418-122-CM26</t>
+          <t>5722-6-CM26</t>
         </is>
       </c>
       <c r="B1190" t="inlineStr">
@@ -77754,17 +77754,17 @@
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1190" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G1190" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H1190" t="inlineStr">
@@ -77774,12 +77774,12 @@
       </c>
       <c r="I1190" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1190" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1190" t="inlineStr">
@@ -77793,7 +77793,7 @@
         </is>
       </c>
       <c r="M1190" s="2" t="n">
-        <v>207.7</v>
+        <v>115.37</v>
       </c>
     </row>
     <row r="1191">
@@ -77994,7 +77994,7 @@
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>5742-48-CM26</t>
+          <t>5742-47-CM26</t>
         </is>
       </c>
       <c r="B1194" t="inlineStr">
@@ -78053,7 +78053,7 @@
         </is>
       </c>
       <c r="M1194" s="2" t="n">
-        <v>125.54</v>
+        <v>121.48</v>
       </c>
     </row>
     <row r="1195">
@@ -78124,7 +78124,7 @@
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>5742-47-CM26</t>
+          <t>5742-48-CM26</t>
         </is>
       </c>
       <c r="B1196" t="inlineStr">
@@ -78183,7 +78183,7 @@
         </is>
       </c>
       <c r="M1196" s="2" t="n">
-        <v>121.48</v>
+        <v>125.54</v>
       </c>
     </row>
     <row r="1197">
@@ -78644,7 +78644,7 @@
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>912853-5-CM26</t>
+          <t>5418-133-CM26</t>
         </is>
       </c>
       <c r="B1204" t="inlineStr">
@@ -78664,17 +78664,17 @@
       </c>
       <c r="E1204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1204" t="inlineStr">
         <is>
-          <t>61.980.570-4</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G1204" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1204" t="inlineStr">
@@ -78684,12 +78684,12 @@
       </c>
       <c r="I1204" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1204" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1204" t="inlineStr">
@@ -78703,13 +78703,13 @@
         </is>
       </c>
       <c r="M1204" s="2" t="n">
-        <v>247.65</v>
+        <v>203.36</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>2180-92-CM26</t>
+          <t>912853-5-CM26</t>
         </is>
       </c>
       <c r="B1205" t="inlineStr">
@@ -78734,12 +78734,12 @@
       </c>
       <c r="F1205" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.980.570-4</t>
         </is>
       </c>
       <c r="G1205" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H1205" t="inlineStr">
@@ -78749,12 +78749,12 @@
       </c>
       <c r="I1205" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1205" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1205" t="inlineStr">
@@ -78768,13 +78768,13 @@
         </is>
       </c>
       <c r="M1205" s="2" t="n">
-        <v>165.38</v>
+        <v>247.65</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>5418-131-CM26</t>
+          <t>2180-92-CM26</t>
         </is>
       </c>
       <c r="B1206" t="inlineStr">
@@ -78794,17 +78794,17 @@
       </c>
       <c r="E1206" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1206" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1206" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1206" t="inlineStr">
@@ -78814,12 +78814,12 @@
       </c>
       <c r="I1206" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1206" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1206" t="inlineStr">
@@ -78833,13 +78833,13 @@
         </is>
       </c>
       <c r="M1206" s="2" t="n">
-        <v>2410.64</v>
+        <v>165.38</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>5418-132-CM26</t>
+          <t>5418-131-CM26</t>
         </is>
       </c>
       <c r="B1207" t="inlineStr">
@@ -78898,13 +78898,13 @@
         </is>
       </c>
       <c r="M1207" s="2" t="n">
-        <v>301.33</v>
+        <v>2410.64</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>5418-133-CM26</t>
+          <t>5418-132-CM26</t>
         </is>
       </c>
       <c r="B1208" t="inlineStr">
@@ -78944,12 +78944,12 @@
       </c>
       <c r="I1208" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1208" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1208" t="inlineStr">
@@ -78963,7 +78963,7 @@
         </is>
       </c>
       <c r="M1208" s="2" t="n">
-        <v>203.36</v>
+        <v>301.33</v>
       </c>
     </row>
     <row r="1209">
@@ -79359,7 +79359,7 @@
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>5418-138-CM26</t>
+          <t>5418-140-CM26</t>
         </is>
       </c>
       <c r="B1215" t="inlineStr">
@@ -79418,7 +79418,7 @@
         </is>
       </c>
       <c r="M1215" s="2" t="n">
-        <v>263.06</v>
+        <v>248.49</v>
       </c>
     </row>
     <row r="1216">
@@ -79489,7 +79489,7 @@
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>5418-139-CM26</t>
+          <t>5418-138-CM26</t>
         </is>
       </c>
       <c r="B1217" t="inlineStr">
@@ -79548,13 +79548,13 @@
         </is>
       </c>
       <c r="M1217" s="2" t="n">
-        <v>238.21</v>
+        <v>263.06</v>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>5418-140-CM26</t>
+          <t>5418-139-CM26</t>
         </is>
       </c>
       <c r="B1218" t="inlineStr">
@@ -79613,13 +79613,13 @@
         </is>
       </c>
       <c r="M1218" s="2" t="n">
-        <v>248.49</v>
+        <v>238.21</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>1283719-93-CM26</t>
+          <t>1057547-9621-CM26</t>
         </is>
       </c>
       <c r="B1219" t="inlineStr">
@@ -79644,12 +79644,12 @@
       </c>
       <c r="F1219" t="inlineStr">
         <is>
-          <t>72.738.600-9</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G1219" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL DE LA ILUSTRE MUNICIPALIDAD DE VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H1219" t="inlineStr">
@@ -79678,13 +79678,13 @@
         </is>
       </c>
       <c r="M1219" s="2" t="n">
-        <v>85.97</v>
+        <v>193.93</v>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>1057547-9621-CM26</t>
+          <t>1283719-90-CM26</t>
         </is>
       </c>
       <c r="B1220" t="inlineStr">
@@ -79709,12 +79709,12 @@
       </c>
       <c r="F1220" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>72.738.600-9</t>
         </is>
       </c>
       <c r="G1220" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>CORPORACION CULTURAL DE LA ILUSTRE MUNICIPALIDAD DE VALDIVIA</t>
         </is>
       </c>
       <c r="H1220" t="inlineStr">
@@ -79743,7 +79743,7 @@
         </is>
       </c>
       <c r="M1220" s="2" t="n">
-        <v>193.93</v>
+        <v>775.52</v>
       </c>
     </row>
     <row r="1221">
@@ -79814,7 +79814,7 @@
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>1283719-90-CM26</t>
+          <t>1283719-92-CM26</t>
         </is>
       </c>
       <c r="B1222" t="inlineStr">
@@ -79873,13 +79873,13 @@
         </is>
       </c>
       <c r="M1222" s="2" t="n">
-        <v>775.52</v>
+        <v>386.85</v>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>1283719-92-CM26</t>
+          <t>1283719-93-CM26</t>
         </is>
       </c>
       <c r="B1223" t="inlineStr">
@@ -79938,7 +79938,7 @@
         </is>
       </c>
       <c r="M1223" s="2" t="n">
-        <v>386.85</v>
+        <v>85.97</v>
       </c>
     </row>
     <row r="1224">
@@ -80659,7 +80659,7 @@
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>4777-537-CM26</t>
+          <t>5740-240-CM26</t>
         </is>
       </c>
       <c r="B1235" t="inlineStr">
@@ -80679,17 +80679,17 @@
       </c>
       <c r="E1235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1235" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G1235" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1235" t="inlineStr">
@@ -80718,13 +80718,13 @@
         </is>
       </c>
       <c r="M1235" s="2" t="n">
-        <v>163.11</v>
+        <v>154.37</v>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>5740-240-CM26</t>
+          <t>4777-537-CM26</t>
         </is>
       </c>
       <c r="B1236" t="inlineStr">
@@ -80744,17 +80744,17 @@
       </c>
       <c r="E1236" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1236" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G1236" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H1236" t="inlineStr">
@@ -80783,7 +80783,7 @@
         </is>
       </c>
       <c r="M1236" s="2" t="n">
-        <v>154.37</v>
+        <v>163.11</v>
       </c>
     </row>
     <row r="1237">
@@ -81439,7 +81439,7 @@
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>1422032-69-CM26</t>
+          <t>1340-386-CM26</t>
         </is>
       </c>
       <c r="B1247" t="inlineStr">
@@ -81464,12 +81464,12 @@
       </c>
       <c r="F1247" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G1247" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H1247" t="inlineStr">
@@ -81498,7 +81498,7 @@
         </is>
       </c>
       <c r="M1247" s="2" t="n">
-        <v>78.94</v>
+        <v>330.95</v>
       </c>
     </row>
     <row r="1248">
@@ -81569,7 +81569,7 @@
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>1340-386-CM26</t>
+          <t>1422032-69-CM26</t>
         </is>
       </c>
       <c r="B1249" t="inlineStr">
@@ -81594,12 +81594,12 @@
       </c>
       <c r="F1249" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G1249" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1249" t="inlineStr">
@@ -81628,7 +81628,7 @@
         </is>
       </c>
       <c r="M1249" s="2" t="n">
-        <v>330.95</v>
+        <v>78.94</v>
       </c>
     </row>
     <row r="1250">
@@ -81699,7 +81699,7 @@
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>1497-159-CM26</t>
+          <t>5877-41-CM26</t>
         </is>
       </c>
       <c r="B1251" t="inlineStr">
@@ -81719,17 +81719,17 @@
       </c>
       <c r="E1251" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1251" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.979.170-3</t>
         </is>
       </c>
       <c r="G1251" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H1251" t="inlineStr">
@@ -81758,13 +81758,13 @@
         </is>
       </c>
       <c r="M1251" s="2" t="n">
-        <v>127.07</v>
+        <v>720.55</v>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>1340-395-CM26</t>
+          <t>1497-159-CM26</t>
         </is>
       </c>
       <c r="B1252" t="inlineStr">
@@ -81784,17 +81784,17 @@
       </c>
       <c r="E1252" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1252" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G1252" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H1252" t="inlineStr">
@@ -81823,13 +81823,13 @@
         </is>
       </c>
       <c r="M1252" s="2" t="n">
-        <v>180.14</v>
+        <v>127.07</v>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>5877-41-CM26</t>
+          <t>1340-395-CM26</t>
         </is>
       </c>
       <c r="B1253" t="inlineStr">
@@ -81854,12 +81854,12 @@
       </c>
       <c r="F1253" t="inlineStr">
         <is>
-          <t>61.979.170-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G1253" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H1253" t="inlineStr">
@@ -81888,7 +81888,7 @@
         </is>
       </c>
       <c r="M1253" s="2" t="n">
-        <v>720.55</v>
+        <v>180.14</v>
       </c>
     </row>
     <row r="1254">
@@ -82024,7 +82024,7 @@
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>1422032-72-CM26</t>
+          <t>1422032-71-CM26</t>
         </is>
       </c>
       <c r="B1256" t="inlineStr">
@@ -82064,12 +82064,12 @@
       </c>
       <c r="I1256" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1256" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1256" t="inlineStr">
@@ -82083,13 +82083,13 @@
         </is>
       </c>
       <c r="M1256" s="2" t="n">
-        <v>134.45</v>
+        <v>60.35</v>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>1422032-71-CM26</t>
+          <t>1422032-72-CM26</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -82129,12 +82129,12 @@
       </c>
       <c r="I1257" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1257" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1257" t="inlineStr">
@@ -82148,13 +82148,13 @@
         </is>
       </c>
       <c r="M1257" s="2" t="n">
-        <v>60.35</v>
+        <v>134.45</v>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>2180-113-CM26</t>
+          <t>881697-10-CM26</t>
         </is>
       </c>
       <c r="B1258" t="inlineStr">
@@ -82174,17 +82174,17 @@
       </c>
       <c r="E1258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1258" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G1258" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H1258" t="inlineStr">
@@ -82194,12 +82194,12 @@
       </c>
       <c r="I1258" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1258" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1258" t="inlineStr">
@@ -82213,13 +82213,13 @@
         </is>
       </c>
       <c r="M1258" s="2" t="n">
-        <v>167.08</v>
+        <v>129.08</v>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>881697-10-CM26</t>
+          <t>2180-113-CM26</t>
         </is>
       </c>
       <c r="B1259" t="inlineStr">
@@ -82239,17 +82239,17 @@
       </c>
       <c r="E1259" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1259" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1259" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1259" t="inlineStr">
@@ -82259,12 +82259,12 @@
       </c>
       <c r="I1259" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1259" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1259" t="inlineStr">
@@ -82278,13 +82278,13 @@
         </is>
       </c>
       <c r="M1259" s="2" t="n">
-        <v>129.08</v>
+        <v>167.08</v>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>2180-114-CM26</t>
+          <t>912853-11-CM26</t>
         </is>
       </c>
       <c r="B1260" t="inlineStr">
@@ -82309,12 +82309,12 @@
       </c>
       <c r="F1260" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.980.570-4</t>
         </is>
       </c>
       <c r="G1260" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H1260" t="inlineStr">
@@ -82343,13 +82343,13 @@
         </is>
       </c>
       <c r="M1260" s="2" t="n">
-        <v>133</v>
+        <v>106.25</v>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>912853-11-CM26</t>
+          <t>2180-114-CM26</t>
         </is>
       </c>
       <c r="B1261" t="inlineStr">
@@ -82374,12 +82374,12 @@
       </c>
       <c r="F1261" t="inlineStr">
         <is>
-          <t>61.980.570-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1261" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1261" t="inlineStr">
@@ -82408,7 +82408,7 @@
         </is>
       </c>
       <c r="M1261" s="2" t="n">
-        <v>106.25</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1262">
@@ -82869,7 +82869,7 @@
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>1271-26-CM26</t>
+          <t>2180-120-CM26</t>
         </is>
       </c>
       <c r="B1269" t="inlineStr">
@@ -82894,12 +82894,12 @@
       </c>
       <c r="F1269" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1269" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1269" t="inlineStr">
@@ -82928,13 +82928,13 @@
         </is>
       </c>
       <c r="M1269" s="2" t="n">
-        <v>182.22</v>
+        <v>125.96</v>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>2180-120-CM26</t>
+          <t>1271-26-CM26</t>
         </is>
       </c>
       <c r="B1270" t="inlineStr">
@@ -82959,12 +82959,12 @@
       </c>
       <c r="F1270" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G1270" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H1270" t="inlineStr">
@@ -82993,7 +82993,7 @@
         </is>
       </c>
       <c r="M1270" s="2" t="n">
-        <v>125.96</v>
+        <v>182.22</v>
       </c>
     </row>
     <row r="1271">
@@ -83519,7 +83519,7 @@
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>3833-500-CM26</t>
+          <t>1208106-59-CM26</t>
         </is>
       </c>
       <c r="B1279" t="inlineStr">
@@ -83539,17 +83539,17 @@
       </c>
       <c r="E1279" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1279" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G1279" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H1279" t="inlineStr">
@@ -83559,12 +83559,12 @@
       </c>
       <c r="I1279" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1279" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1279" t="inlineStr">
@@ -83578,13 +83578,13 @@
         </is>
       </c>
       <c r="M1279" s="2" t="n">
-        <v>94.39</v>
+        <v>92.15000000000001</v>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>5751-196-CM26</t>
+          <t>2281-1037-CM26</t>
         </is>
       </c>
       <c r="B1280" t="inlineStr">
@@ -83609,12 +83609,12 @@
       </c>
       <c r="F1280" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G1280" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H1280" t="inlineStr">
@@ -83624,12 +83624,12 @@
       </c>
       <c r="I1280" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1280" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1280" t="inlineStr">
@@ -83643,13 +83643,13 @@
         </is>
       </c>
       <c r="M1280" s="2" t="n">
-        <v>193.76</v>
+        <v>137.04</v>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>1208106-59-CM26</t>
+          <t>5751-196-CM26</t>
         </is>
       </c>
       <c r="B1281" t="inlineStr">
@@ -83674,12 +83674,12 @@
       </c>
       <c r="F1281" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G1281" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H1281" t="inlineStr">
@@ -83708,13 +83708,13 @@
         </is>
       </c>
       <c r="M1281" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>193.76</v>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>3833-501-CM26</t>
+          <t>3833-500-CM26</t>
         </is>
       </c>
       <c r="B1282" t="inlineStr">
@@ -83773,13 +83773,13 @@
         </is>
       </c>
       <c r="M1282" s="2" t="n">
-        <v>154.66</v>
+        <v>94.39</v>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>2281-1037-CM26</t>
+          <t>3833-501-CM26</t>
         </is>
       </c>
       <c r="B1283" t="inlineStr">
@@ -83799,17 +83799,17 @@
       </c>
       <c r="E1283" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1283" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G1283" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H1283" t="inlineStr">
@@ -83838,7 +83838,7 @@
         </is>
       </c>
       <c r="M1283" s="2" t="n">
-        <v>137.04</v>
+        <v>154.66</v>
       </c>
     </row>
     <row r="1284">
@@ -84299,7 +84299,7 @@
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>2180-125-CM26</t>
+          <t>2180-127-CM26</t>
         </is>
       </c>
       <c r="B1291" t="inlineStr">
@@ -84358,13 +84358,13 @@
         </is>
       </c>
       <c r="M1291" s="2" t="n">
-        <v>132.06</v>
+        <v>162.22</v>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>5742-81-CM26</t>
+          <t>5418-176-CM26</t>
         </is>
       </c>
       <c r="B1292" t="inlineStr">
@@ -84389,12 +84389,12 @@
       </c>
       <c r="F1292" t="inlineStr">
         <is>
-          <t>61.979.040-5</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G1292" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1292" t="inlineStr">
@@ -84423,13 +84423,13 @@
         </is>
       </c>
       <c r="M1292" s="2" t="n">
-        <v>380.89</v>
+        <v>272.26</v>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>5418-176-CM26</t>
+          <t>5418-177-CM26</t>
         </is>
       </c>
       <c r="B1293" t="inlineStr">
@@ -84469,12 +84469,12 @@
       </c>
       <c r="I1293" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1293" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1293" t="inlineStr">
@@ -84488,13 +84488,13 @@
         </is>
       </c>
       <c r="M1293" s="2" t="n">
-        <v>272.26</v>
+        <v>154</v>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>2180-127-CM26</t>
+          <t>2180-125-CM26</t>
         </is>
       </c>
       <c r="B1294" t="inlineStr">
@@ -84553,13 +84553,13 @@
         </is>
       </c>
       <c r="M1294" s="2" t="n">
-        <v>162.22</v>
+        <v>132.06</v>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>5418-177-CM26</t>
+          <t>5742-81-CM26</t>
         </is>
       </c>
       <c r="B1295" t="inlineStr">
@@ -84584,12 +84584,12 @@
       </c>
       <c r="F1295" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.979.040-5</t>
         </is>
       </c>
       <c r="G1295" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H1295" t="inlineStr">
@@ -84599,12 +84599,12 @@
       </c>
       <c r="I1295" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1295" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1295" t="inlineStr">
@@ -84618,7 +84618,7 @@
         </is>
       </c>
       <c r="M1295" s="2" t="n">
-        <v>154</v>
+        <v>380.89</v>
       </c>
     </row>
     <row r="1296">
@@ -84884,7 +84884,7 @@
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>620039-13-CM26</t>
+          <t>2180-131-CM26</t>
         </is>
       </c>
       <c r="B1300" t="inlineStr">
@@ -84904,17 +84904,17 @@
       </c>
       <c r="E1300" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1300" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1300" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1300" t="inlineStr">
@@ -84943,7 +84943,7 @@
         </is>
       </c>
       <c r="M1300" s="2" t="n">
-        <v>522.7</v>
+        <v>171.5</v>
       </c>
     </row>
     <row r="1301">
@@ -85014,7 +85014,7 @@
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>2180-131-CM26</t>
+          <t>620039-13-CM26</t>
         </is>
       </c>
       <c r="B1302" t="inlineStr">
@@ -85034,17 +85034,17 @@
       </c>
       <c r="E1302" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1302" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G1302" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H1302" t="inlineStr">
@@ -85073,7 +85073,7 @@
         </is>
       </c>
       <c r="M1302" s="2" t="n">
-        <v>171.5</v>
+        <v>522.7</v>
       </c>
     </row>
     <row r="1303">
@@ -85209,7 +85209,7 @@
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>5751-212-CM26</t>
+          <t>5751-213-CM26</t>
         </is>
       </c>
       <c r="B1305" t="inlineStr">
@@ -85268,7 +85268,7 @@
         </is>
       </c>
       <c r="M1305" s="2" t="n">
-        <v>94.20999999999999</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="1306">
@@ -85469,7 +85469,7 @@
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>5751-213-CM26</t>
+          <t>5751-212-CM26</t>
         </is>
       </c>
       <c r="B1309" t="inlineStr">
@@ -85528,7 +85528,7 @@
         </is>
       </c>
       <c r="M1309" s="2" t="n">
-        <v>46.08</v>
+        <v>94.20999999999999</v>
       </c>
     </row>
     <row r="1310">
@@ -85729,7 +85729,7 @@
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>5740-301-CM26</t>
+          <t>5740-302-CM26</t>
         </is>
       </c>
       <c r="B1313" t="inlineStr">
@@ -85788,13 +85788,13 @@
         </is>
       </c>
       <c r="M1313" s="2" t="n">
-        <v>372.23</v>
+        <v>444.55</v>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>5740-302-CM26</t>
+          <t>5740-305-CM26</t>
         </is>
       </c>
       <c r="B1314" t="inlineStr">
@@ -85834,12 +85834,12 @@
       </c>
       <c r="I1314" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1314" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1314" t="inlineStr">
@@ -85853,13 +85853,13 @@
         </is>
       </c>
       <c r="M1314" s="2" t="n">
-        <v>444.55</v>
+        <v>254.99</v>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>5740-305-CM26</t>
+          <t>5740-301-CM26</t>
         </is>
       </c>
       <c r="B1315" t="inlineStr">
@@ -85899,12 +85899,12 @@
       </c>
       <c r="I1315" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1315" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1315" t="inlineStr">
@@ -85918,13 +85918,13 @@
         </is>
       </c>
       <c r="M1315" s="2" t="n">
-        <v>254.99</v>
+        <v>372.23</v>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>5740-308-CM26</t>
+          <t>5877-50-CM26</t>
         </is>
       </c>
       <c r="B1316" t="inlineStr">
@@ -85949,12 +85949,12 @@
       </c>
       <c r="F1316" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>61.979.170-3</t>
         </is>
       </c>
       <c r="G1316" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H1316" t="inlineStr">
@@ -85983,13 +85983,13 @@
         </is>
       </c>
       <c r="M1316" s="2" t="n">
-        <v>141.48</v>
+        <v>172.98</v>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>5877-50-CM26</t>
+          <t>5740-308-CM26</t>
         </is>
       </c>
       <c r="B1317" t="inlineStr">
@@ -86014,12 +86014,12 @@
       </c>
       <c r="F1317" t="inlineStr">
         <is>
-          <t>61.979.170-3</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G1317" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1317" t="inlineStr">
@@ -86048,7 +86048,7 @@
         </is>
       </c>
       <c r="M1317" s="2" t="n">
-        <v>172.98</v>
+        <v>141.48</v>
       </c>
     </row>
     <row r="1318">
@@ -86184,7 +86184,7 @@
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>1057547-12753-CM26</t>
+          <t>4777-679-CM26</t>
         </is>
       </c>
       <c r="B1320" t="inlineStr">
@@ -86204,17 +86204,17 @@
       </c>
       <c r="E1320" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1320" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G1320" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H1320" t="inlineStr">
@@ -86243,13 +86243,13 @@
         </is>
       </c>
       <c r="M1320" s="2" t="n">
-        <v>211.08</v>
+        <v>269.52</v>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>4777-679-CM26</t>
+          <t>1057547-12753-CM26</t>
         </is>
       </c>
       <c r="B1321" t="inlineStr">
@@ -86269,17 +86269,17 @@
       </c>
       <c r="E1321" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1321" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G1321" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H1321" t="inlineStr">
@@ -86308,7 +86308,7 @@
         </is>
       </c>
       <c r="M1321" s="2" t="n">
-        <v>269.52</v>
+        <v>211.08</v>
       </c>
     </row>
     <row r="1322">
@@ -86379,7 +86379,7 @@
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>5740-312-CM26</t>
+          <t>952946-166-CM26</t>
         </is>
       </c>
       <c r="B1323" t="inlineStr">
@@ -86404,12 +86404,12 @@
       </c>
       <c r="F1323" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G1323" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1323" t="inlineStr">
@@ -86438,13 +86438,13 @@
         </is>
       </c>
       <c r="M1323" s="2" t="n">
-        <v>235.35</v>
+        <v>220.44</v>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>952946-166-CM26</t>
+          <t>5740-312-CM26</t>
         </is>
       </c>
       <c r="B1324" t="inlineStr">
@@ -86469,12 +86469,12 @@
       </c>
       <c r="F1324" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G1324" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1324" t="inlineStr">
@@ -86503,13 +86503,13 @@
         </is>
       </c>
       <c r="M1324" s="2" t="n">
-        <v>220.44</v>
+        <v>235.35</v>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>1057547-12893-CM26</t>
+          <t>5418-194-CM26</t>
         </is>
       </c>
       <c r="B1325" t="inlineStr">
@@ -86534,12 +86534,12 @@
       </c>
       <c r="F1325" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G1325" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1325" t="inlineStr">
@@ -86549,12 +86549,12 @@
       </c>
       <c r="I1325" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1325" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1325" t="inlineStr">
@@ -86568,13 +86568,13 @@
         </is>
       </c>
       <c r="M1325" s="2" t="n">
-        <v>172.35</v>
+        <v>228.54</v>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>5657-240-CM26</t>
+          <t>1057547-12893-CM26</t>
         </is>
       </c>
       <c r="B1326" t="inlineStr">
@@ -86594,17 +86594,17 @@
       </c>
       <c r="E1326" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1326" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G1326" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H1326" t="inlineStr">
@@ -86614,12 +86614,12 @@
       </c>
       <c r="I1326" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1326" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1326" t="inlineStr">
@@ -86633,13 +86633,13 @@
         </is>
       </c>
       <c r="M1326" s="2" t="n">
-        <v>141.17</v>
+        <v>172.35</v>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>5418-194-CM26</t>
+          <t>5657-240-CM26</t>
         </is>
       </c>
       <c r="B1327" t="inlineStr">
@@ -86659,17 +86659,17 @@
       </c>
       <c r="E1327" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1327" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G1327" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H1327" t="inlineStr">
@@ -86698,13 +86698,13 @@
         </is>
       </c>
       <c r="M1327" s="2" t="n">
-        <v>228.54</v>
+        <v>141.17</v>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>2180-145-CM26</t>
+          <t>5877-53-CM26</t>
         </is>
       </c>
       <c r="B1328" t="inlineStr">
@@ -86724,17 +86724,17 @@
       </c>
       <c r="E1328" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1328" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.979.170-3</t>
         </is>
       </c>
       <c r="G1328" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H1328" t="inlineStr">
@@ -86763,7 +86763,7 @@
         </is>
       </c>
       <c r="M1328" s="2" t="n">
-        <v>287.04</v>
+        <v>518.7</v>
       </c>
     </row>
     <row r="1329">
@@ -86834,7 +86834,7 @@
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>5877-53-CM26</t>
+          <t>2180-145-CM26</t>
         </is>
       </c>
       <c r="B1330" t="inlineStr">
@@ -86854,17 +86854,17 @@
       </c>
       <c r="E1330" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1330" t="inlineStr">
         <is>
-          <t>61.979.170-3</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1330" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1330" t="inlineStr">
@@ -86893,13 +86893,13 @@
         </is>
       </c>
       <c r="M1330" s="2" t="n">
-        <v>518.7</v>
+        <v>287.04</v>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>1305560-78-CM26</t>
+          <t>1035685-269-CM26</t>
         </is>
       </c>
       <c r="B1331" t="inlineStr">
@@ -86919,17 +86919,17 @@
       </c>
       <c r="E1331" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1331" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G1331" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1331" t="inlineStr">
@@ -86939,12 +86939,12 @@
       </c>
       <c r="I1331" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1331" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1331" t="inlineStr">
@@ -86958,13 +86958,13 @@
         </is>
       </c>
       <c r="M1331" s="2" t="n">
-        <v>134.13</v>
+        <v>73.61</v>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>1305560-77-CM26</t>
+          <t>1035685-270-CM26</t>
         </is>
       </c>
       <c r="B1332" t="inlineStr">
@@ -86984,17 +86984,17 @@
       </c>
       <c r="E1332" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1332" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G1332" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1332" t="inlineStr">
@@ -87004,12 +87004,12 @@
       </c>
       <c r="I1332" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1332" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1332" t="inlineStr">
@@ -87023,13 +87023,13 @@
         </is>
       </c>
       <c r="M1332" s="2" t="n">
-        <v>109.32</v>
+        <v>246.92</v>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>1035685-270-CM26</t>
+          <t>1035685-271-CM26</t>
         </is>
       </c>
       <c r="B1333" t="inlineStr">
@@ -87069,12 +87069,12 @@
       </c>
       <c r="I1333" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1333" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1333" t="inlineStr">
@@ -87088,13 +87088,13 @@
         </is>
       </c>
       <c r="M1333" s="2" t="n">
-        <v>246.92</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>1035685-269-CM26</t>
+          <t>1305560-77-CM26</t>
         </is>
       </c>
       <c r="B1334" t="inlineStr">
@@ -87114,17 +87114,17 @@
       </c>
       <c r="E1334" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1334" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G1334" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H1334" t="inlineStr">
@@ -87134,12 +87134,12 @@
       </c>
       <c r="I1334" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1334" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1334" t="inlineStr">
@@ -87153,13 +87153,13 @@
         </is>
       </c>
       <c r="M1334" s="2" t="n">
-        <v>73.61</v>
+        <v>109.32</v>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>1035685-271-CM26</t>
+          <t>1305560-78-CM26</t>
         </is>
       </c>
       <c r="B1335" t="inlineStr">
@@ -87179,17 +87179,17 @@
       </c>
       <c r="E1335" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1335" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G1335" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H1335" t="inlineStr">
@@ -87218,13 +87218,13 @@
         </is>
       </c>
       <c r="M1335" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>134.13</v>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>1057547-13096-CM26</t>
+          <t>5795-75-CM26</t>
         </is>
       </c>
       <c r="B1336" t="inlineStr">
@@ -87244,17 +87244,17 @@
       </c>
       <c r="E1336" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1336" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.979.130-4</t>
         </is>
       </c>
       <c r="G1336" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H1336" t="inlineStr">
@@ -87264,12 +87264,12 @@
       </c>
       <c r="I1336" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1336" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1336" t="inlineStr">
@@ -87283,13 +87283,13 @@
         </is>
       </c>
       <c r="M1336" s="2" t="n">
-        <v>96.93000000000001</v>
+        <v>302.38</v>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>5795-75-CM26</t>
+          <t>1057547-13096-CM26</t>
         </is>
       </c>
       <c r="B1337" t="inlineStr">
@@ -87309,17 +87309,17 @@
       </c>
       <c r="E1337" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1337" t="inlineStr">
         <is>
-          <t>61.979.130-4</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G1337" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H1337" t="inlineStr">
@@ -87329,12 +87329,12 @@
       </c>
       <c r="I1337" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1337" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1337" t="inlineStr">
@@ -87348,7 +87348,7 @@
         </is>
       </c>
       <c r="M1337" s="2" t="n">
-        <v>302.38</v>
+        <v>96.93000000000001</v>
       </c>
     </row>
     <row r="1338">
@@ -87484,7 +87484,7 @@
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>1283719-129-CM26</t>
+          <t>1283719-131-CM26</t>
         </is>
       </c>
       <c r="B1340" t="inlineStr">
@@ -87543,13 +87543,13 @@
         </is>
       </c>
       <c r="M1340" s="2" t="n">
-        <v>87.14</v>
+        <v>718.8099999999999</v>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>1283719-130-CM26</t>
+          <t>1283719-129-CM26</t>
         </is>
       </c>
       <c r="B1341" t="inlineStr">
@@ -87608,13 +87608,13 @@
         </is>
       </c>
       <c r="M1341" s="2" t="n">
-        <v>221.53</v>
+        <v>87.14</v>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>1283719-131-CM26</t>
+          <t>1283719-130-CM26</t>
         </is>
       </c>
       <c r="B1342" t="inlineStr">
@@ -87673,7 +87673,7 @@
         </is>
       </c>
       <c r="M1342" s="2" t="n">
-        <v>718.8099999999999</v>
+        <v>221.53</v>
       </c>
     </row>
     <row r="1343">
@@ -87874,7 +87874,7 @@
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>1283719-140-CM26</t>
+          <t>1283719-138-CM26</t>
         </is>
       </c>
       <c r="B1346" t="inlineStr">
@@ -87914,12 +87914,12 @@
       </c>
       <c r="I1346" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1346" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1346" t="inlineStr">
@@ -87933,13 +87933,13 @@
         </is>
       </c>
       <c r="M1346" s="2" t="n">
-        <v>112.38</v>
+        <v>215.38</v>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>1283719-141-CM26</t>
+          <t>1283719-140-CM26</t>
         </is>
       </c>
       <c r="B1347" t="inlineStr">
@@ -87979,12 +87979,12 @@
       </c>
       <c r="I1347" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1347" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1347" t="inlineStr">
@@ -87998,13 +87998,13 @@
         </is>
       </c>
       <c r="M1347" s="2" t="n">
-        <v>64.12</v>
+        <v>112.38</v>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>1283719-138-CM26</t>
+          <t>1283719-141-CM26</t>
         </is>
       </c>
       <c r="B1348" t="inlineStr">
@@ -88063,7 +88063,7 @@
         </is>
       </c>
       <c r="M1348" s="2" t="n">
-        <v>215.38</v>
+        <v>64.12</v>
       </c>
     </row>
     <row r="1349">
@@ -88264,7 +88264,7 @@
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>1422032-94-CM26</t>
+          <t>5877-57-CM26</t>
         </is>
       </c>
       <c r="B1352" t="inlineStr">
@@ -88284,17 +88284,17 @@
       </c>
       <c r="E1352" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1352" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>61.979.170-3</t>
         </is>
       </c>
       <c r="G1352" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H1352" t="inlineStr">
@@ -88323,13 +88323,13 @@
         </is>
       </c>
       <c r="M1352" s="2" t="n">
-        <v>163.64</v>
+        <v>762.55</v>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>1422032-93-CM26</t>
+          <t>1283719-144-CM26</t>
         </is>
       </c>
       <c r="B1353" t="inlineStr">
@@ -88349,17 +88349,17 @@
       </c>
       <c r="E1353" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1353" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>72.738.600-9</t>
         </is>
       </c>
       <c r="G1353" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>CORPORACION CULTURAL DE LA ILUSTRE MUNICIPALIDAD DE VALDIVIA</t>
         </is>
       </c>
       <c r="H1353" t="inlineStr">
@@ -88388,13 +88388,13 @@
         </is>
       </c>
       <c r="M1353" s="2" t="n">
-        <v>187.74</v>
+        <v>225.35</v>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>952946-171-CM26</t>
+          <t>1422032-94-CM26</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -88419,12 +88419,12 @@
       </c>
       <c r="F1354" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G1354" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1354" t="inlineStr">
@@ -88453,13 +88453,13 @@
         </is>
       </c>
       <c r="M1354" s="2" t="n">
-        <v>159.96</v>
+        <v>163.64</v>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>1283719-144-CM26</t>
+          <t>1422032-93-CM26</t>
         </is>
       </c>
       <c r="B1355" t="inlineStr">
@@ -88479,17 +88479,17 @@
       </c>
       <c r="E1355" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1355" t="inlineStr">
         <is>
-          <t>72.738.600-9</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G1355" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL DE LA ILUSTRE MUNICIPALIDAD DE VALDIVIA</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1355" t="inlineStr">
@@ -88518,13 +88518,13 @@
         </is>
       </c>
       <c r="M1355" s="2" t="n">
-        <v>225.35</v>
+        <v>187.74</v>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>5877-57-CM26</t>
+          <t>952946-171-CM26</t>
         </is>
       </c>
       <c r="B1356" t="inlineStr">
@@ -88544,17 +88544,17 @@
       </c>
       <c r="E1356" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1356" t="inlineStr">
         <is>
-          <t>61.979.170-3</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G1356" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1356" t="inlineStr">
@@ -88583,13 +88583,13 @@
         </is>
       </c>
       <c r="M1356" s="2" t="n">
-        <v>762.55</v>
+        <v>159.96</v>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>1035685-275-CM26</t>
+          <t>5877-59-CM26</t>
         </is>
       </c>
       <c r="B1357" t="inlineStr">
@@ -88609,17 +88609,17 @@
       </c>
       <c r="E1357" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1357" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.979.170-3</t>
         </is>
       </c>
       <c r="G1357" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H1357" t="inlineStr">
@@ -88648,7 +88648,7 @@
         </is>
       </c>
       <c r="M1357" s="2" t="n">
-        <v>635.27</v>
+        <v>166.53</v>
       </c>
     </row>
     <row r="1358">
@@ -88719,7 +88719,7 @@
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>508994-38-CM26</t>
+          <t>1035685-275-CM26</t>
         </is>
       </c>
       <c r="B1359" t="inlineStr">
@@ -88739,17 +88739,17 @@
       </c>
       <c r="E1359" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1359" t="inlineStr">
         <is>
-          <t>61.979.160-6</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G1359" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1359" t="inlineStr">
@@ -88778,13 +88778,13 @@
         </is>
       </c>
       <c r="M1359" s="2" t="n">
-        <v>253.31</v>
+        <v>635.27</v>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>5877-59-CM26</t>
+          <t>508994-38-CM26</t>
         </is>
       </c>
       <c r="B1360" t="inlineStr">
@@ -88809,12 +88809,12 @@
       </c>
       <c r="F1360" t="inlineStr">
         <is>
-          <t>61.979.170-3</t>
+          <t>61.979.160-6</t>
         </is>
       </c>
       <c r="G1360" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H1360" t="inlineStr">
@@ -88843,13 +88843,13 @@
         </is>
       </c>
       <c r="M1360" s="2" t="n">
-        <v>166.53</v>
+        <v>253.31</v>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>2905-621-CM26</t>
+          <t>4777-731-CM26</t>
         </is>
       </c>
       <c r="B1361" t="inlineStr">
@@ -88874,12 +88874,12 @@
       </c>
       <c r="F1361" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G1361" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H1361" t="inlineStr">
@@ -88908,13 +88908,13 @@
         </is>
       </c>
       <c r="M1361" s="2" t="n">
-        <v>1675.84</v>
+        <v>344.38</v>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>4777-730-CM26</t>
+          <t>2905-621-CM26</t>
         </is>
       </c>
       <c r="B1362" t="inlineStr">
@@ -88939,12 +88939,12 @@
       </c>
       <c r="F1362" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G1362" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H1362" t="inlineStr">
@@ -88973,13 +88973,13 @@
         </is>
       </c>
       <c r="M1362" s="2" t="n">
-        <v>582.73</v>
+        <v>1675.84</v>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>4777-731-CM26</t>
+          <t>4777-730-CM26</t>
         </is>
       </c>
       <c r="B1363" t="inlineStr">
@@ -89038,7 +89038,7 @@
         </is>
       </c>
       <c r="M1363" s="2" t="n">
-        <v>344.38</v>
+        <v>582.73</v>
       </c>
     </row>
     <row r="1364">
@@ -89239,7 +89239,7 @@
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>1057547-13578-CM26</t>
+          <t>5418-212-CM26</t>
         </is>
       </c>
       <c r="B1367" t="inlineStr">
@@ -89264,12 +89264,12 @@
       </c>
       <c r="F1367" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G1367" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1367" t="inlineStr">
@@ -89279,12 +89279,12 @@
       </c>
       <c r="I1367" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1367" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1367" t="inlineStr">
@@ -89298,13 +89298,13 @@
         </is>
       </c>
       <c r="M1367" s="2" t="n">
-        <v>207.66</v>
+        <v>284.11</v>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>5418-212-CM26</t>
+          <t>1057547-13578-CM26</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
@@ -89329,12 +89329,12 @@
       </c>
       <c r="F1368" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G1368" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H1368" t="inlineStr">
@@ -89344,12 +89344,12 @@
       </c>
       <c r="I1368" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1368" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1368" t="inlineStr">
@@ -89363,7 +89363,7 @@
         </is>
       </c>
       <c r="M1368" s="2" t="n">
-        <v>284.11</v>
+        <v>207.66</v>
       </c>
     </row>
     <row r="1369">
@@ -89499,7 +89499,7 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>2180-152-CM26</t>
+          <t>1057547-13714-CM26</t>
         </is>
       </c>
       <c r="B1371" t="inlineStr">
@@ -89519,17 +89519,17 @@
       </c>
       <c r="E1371" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1371" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G1371" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H1371" t="inlineStr">
@@ -89558,13 +89558,13 @@
         </is>
       </c>
       <c r="M1371" s="2" t="n">
-        <v>257.02</v>
+        <v>409.17</v>
       </c>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>1057547-13714-CM26</t>
+          <t>523524-20-CM26</t>
         </is>
       </c>
       <c r="B1372" t="inlineStr">
@@ -89589,12 +89589,12 @@
       </c>
       <c r="F1372" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G1372" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H1372" t="inlineStr">
@@ -89623,13 +89623,13 @@
         </is>
       </c>
       <c r="M1372" s="2" t="n">
-        <v>409.17</v>
+        <v>267.7</v>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>523524-20-CM26</t>
+          <t>2180-152-CM26</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr">
@@ -89649,17 +89649,17 @@
       </c>
       <c r="E1373" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1373" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1373" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1373" t="inlineStr">
@@ -89688,7 +89688,7 @@
         </is>
       </c>
       <c r="M1373" s="2" t="n">
-        <v>267.7</v>
+        <v>257.02</v>
       </c>
     </row>
     <row r="1374">
@@ -89759,7 +89759,7 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>1491-69-CM26</t>
+          <t>1057547-13851-CM26</t>
         </is>
       </c>
       <c r="B1375" t="inlineStr">
@@ -89779,17 +89779,17 @@
       </c>
       <c r="E1375" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1375" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G1375" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H1375" t="inlineStr">
@@ -89818,13 +89818,13 @@
         </is>
       </c>
       <c r="M1375" s="2" t="n">
-        <v>197.03</v>
+        <v>148.63</v>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>1057547-13851-CM26</t>
+          <t>1491-69-CM26</t>
         </is>
       </c>
       <c r="B1376" t="inlineStr">
@@ -89844,17 +89844,17 @@
       </c>
       <c r="E1376" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1376" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G1376" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H1376" t="inlineStr">
@@ -89883,7 +89883,7 @@
         </is>
       </c>
       <c r="M1376" s="2" t="n">
-        <v>148.63</v>
+        <v>197.03</v>
       </c>
     </row>
     <row r="1377">
@@ -90214,7 +90214,7 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>2180-158-CM26</t>
+          <t>5740-344-CM26</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr">
@@ -90234,17 +90234,17 @@
       </c>
       <c r="E1382" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1382" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G1382" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1382" t="inlineStr">
@@ -90254,12 +90254,12 @@
       </c>
       <c r="I1382" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1382" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1382" t="inlineStr">
@@ -90273,13 +90273,13 @@
         </is>
       </c>
       <c r="M1382" s="2" t="n">
-        <v>160.42</v>
+        <v>294.29</v>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>5740-344-CM26</t>
+          <t>5740-345-CM26</t>
         </is>
       </c>
       <c r="B1383" t="inlineStr">
@@ -90338,13 +90338,13 @@
         </is>
       </c>
       <c r="M1383" s="2" t="n">
-        <v>294.29</v>
+        <v>140.02</v>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>5740-345-CM26</t>
+          <t>2180-156-CM26</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
@@ -90364,17 +90364,17 @@
       </c>
       <c r="E1384" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1384" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1384" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1384" t="inlineStr">
@@ -90403,13 +90403,13 @@
         </is>
       </c>
       <c r="M1384" s="2" t="n">
-        <v>140.02</v>
+        <v>282.69</v>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>2180-156-CM26</t>
+          <t>2180-157-CM26</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
@@ -90468,13 +90468,13 @@
         </is>
       </c>
       <c r="M1385" s="2" t="n">
-        <v>282.69</v>
+        <v>137.46</v>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>2180-157-CM26</t>
+          <t>2180-158-CM26</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
@@ -90514,12 +90514,12 @@
       </c>
       <c r="I1386" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1386" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1386" t="inlineStr">
@@ -90533,7 +90533,7 @@
         </is>
       </c>
       <c r="M1386" s="2" t="n">
-        <v>137.46</v>
+        <v>160.42</v>
       </c>
     </row>
     <row r="1387">
@@ -90604,7 +90604,7 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>613925-25-CM26</t>
+          <t>1432083-2286-CM26</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
@@ -90624,17 +90624,17 @@
       </c>
       <c r="E1388" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1388" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G1388" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H1388" t="inlineStr">
@@ -90663,13 +90663,13 @@
         </is>
       </c>
       <c r="M1388" s="2" t="n">
-        <v>249.37</v>
+        <v>395.23</v>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>1432083-2285-CM26</t>
+          <t>613925-25-CM26</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
@@ -90689,17 +90689,17 @@
       </c>
       <c r="E1389" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1389" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G1389" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H1389" t="inlineStr">
@@ -90728,13 +90728,13 @@
         </is>
       </c>
       <c r="M1389" s="2" t="n">
-        <v>620.5</v>
+        <v>249.37</v>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>5740-348-CM26</t>
+          <t>5418-223-CM26</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
@@ -90759,12 +90759,12 @@
       </c>
       <c r="F1390" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G1390" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1390" t="inlineStr">
@@ -90793,13 +90793,13 @@
         </is>
       </c>
       <c r="M1390" s="2" t="n">
-        <v>201.28</v>
+        <v>270.92</v>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>5418-222-CM26</t>
+          <t>5740-348-CM26</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr">
@@ -90824,12 +90824,12 @@
       </c>
       <c r="F1391" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G1391" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1391" t="inlineStr">
@@ -90858,13 +90858,13 @@
         </is>
       </c>
       <c r="M1391" s="2" t="n">
-        <v>265.91</v>
+        <v>201.28</v>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>5418-221-CM26</t>
+          <t>5418-222-CM26</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
@@ -90923,13 +90923,13 @@
         </is>
       </c>
       <c r="M1392" s="2" t="n">
-        <v>511.35</v>
+        <v>265.91</v>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>1432083-2286-CM26</t>
+          <t>1432083-2285-CM26</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
@@ -90988,13 +90988,13 @@
         </is>
       </c>
       <c r="M1393" s="2" t="n">
-        <v>395.23</v>
+        <v>620.5</v>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>5418-223-CM26</t>
+          <t>5418-221-CM26</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
@@ -91053,13 +91053,13 @@
         </is>
       </c>
       <c r="M1394" s="2" t="n">
-        <v>270.92</v>
+        <v>511.35</v>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>1422032-109-CM26</t>
+          <t>3623-486-CM26</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
@@ -91079,17 +91079,17 @@
       </c>
       <c r="E1395" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1395" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>69.200.500-7</t>
         </is>
       </c>
       <c r="G1395" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE MAFIL</t>
         </is>
       </c>
       <c r="H1395" t="inlineStr">
@@ -91118,13 +91118,13 @@
         </is>
       </c>
       <c r="M1395" s="2" t="n">
-        <v>717.01</v>
+        <v>165.57</v>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>1057547-14052-CM26</t>
+          <t>299-177-CM26</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
@@ -91149,12 +91149,12 @@
       </c>
       <c r="F1396" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G1396" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H1396" t="inlineStr">
@@ -91164,12 +91164,12 @@
       </c>
       <c r="I1396" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1396" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1396" t="inlineStr">
@@ -91183,13 +91183,13 @@
         </is>
       </c>
       <c r="M1396" s="2" t="n">
-        <v>173.18</v>
+        <v>303.18</v>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>5657-258-CM26</t>
+          <t>1057547-14052-CM26</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
@@ -91214,12 +91214,12 @@
       </c>
       <c r="F1397" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G1397" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H1397" t="inlineStr">
@@ -91229,12 +91229,12 @@
       </c>
       <c r="I1397" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1397" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1397" t="inlineStr">
@@ -91248,13 +91248,13 @@
         </is>
       </c>
       <c r="M1397" s="2" t="n">
-        <v>50.16</v>
+        <v>173.18</v>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>3623-486-CM26</t>
+          <t>1422032-109-CM26</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
@@ -91274,17 +91274,17 @@
       </c>
       <c r="E1398" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1398" t="inlineStr">
         <is>
-          <t>69.200.500-7</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G1398" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAFIL</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1398" t="inlineStr">
@@ -91313,13 +91313,13 @@
         </is>
       </c>
       <c r="M1398" s="2" t="n">
-        <v>165.57</v>
+        <v>717.01</v>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>5657-257-CM26</t>
+          <t>5657-258-CM26</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
@@ -91378,13 +91378,13 @@
         </is>
       </c>
       <c r="M1399" s="2" t="n">
-        <v>46.19</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>299-177-CM26</t>
+          <t>5657-257-CM26</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
@@ -91409,12 +91409,12 @@
       </c>
       <c r="F1400" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G1400" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H1400" t="inlineStr">
@@ -91443,7 +91443,7 @@
         </is>
       </c>
       <c r="M1400" s="2" t="n">
-        <v>303.18</v>
+        <v>46.19</v>
       </c>
     </row>
     <row r="1401">
@@ -91514,7 +91514,7 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>299-183-CM26</t>
+          <t>2905-684-CM26</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
@@ -91539,12 +91539,12 @@
       </c>
       <c r="F1402" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G1402" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H1402" t="inlineStr">
@@ -91554,12 +91554,12 @@
       </c>
       <c r="I1402" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1402" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1402" t="inlineStr">
@@ -91573,13 +91573,13 @@
         </is>
       </c>
       <c r="M1402" s="2" t="n">
-        <v>154.11</v>
+        <v>1738.31</v>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>2905-684-CM26</t>
+          <t>2905-685-CM26</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
@@ -91619,12 +91619,12 @@
       </c>
       <c r="I1403" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1403" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1403" t="inlineStr">
@@ -91638,13 +91638,13 @@
         </is>
       </c>
       <c r="M1403" s="2" t="n">
-        <v>1738.31</v>
+        <v>1297.9</v>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>2905-685-CM26</t>
+          <t>299-183-CM26</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
@@ -91669,12 +91669,12 @@
       </c>
       <c r="F1404" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G1404" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H1404" t="inlineStr">
@@ -91703,7 +91703,7 @@
         </is>
       </c>
       <c r="M1404" s="2" t="n">
-        <v>1297.9</v>
+        <v>154.11</v>
       </c>
     </row>
     <row r="1405">
@@ -92034,7 +92034,7 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>1497-244-CM26</t>
+          <t>1497-243-CM26</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
@@ -92093,13 +92093,13 @@
         </is>
       </c>
       <c r="M1410" s="2" t="n">
-        <v>59.48</v>
+        <v>182.26</v>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>1497-243-CM26</t>
+          <t>1497-244-CM26</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
@@ -92158,7 +92158,7 @@
         </is>
       </c>
       <c r="M1411" s="2" t="n">
-        <v>182.26</v>
+        <v>59.48</v>
       </c>
     </row>
     <row r="1412">
@@ -92229,7 +92229,7 @@
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>1422032-116-CM26</t>
+          <t>4777-798-CM26</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
@@ -92254,12 +92254,12 @@
       </c>
       <c r="F1413" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G1413" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H1413" t="inlineStr">
@@ -92288,13 +92288,13 @@
         </is>
       </c>
       <c r="M1413" s="2" t="n">
-        <v>245.21</v>
+        <v>340.09</v>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>4777-798-CM26</t>
+          <t>1422032-116-CM26</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
@@ -92319,12 +92319,12 @@
       </c>
       <c r="F1414" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G1414" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1414" t="inlineStr">
@@ -92353,13 +92353,13 @@
         </is>
       </c>
       <c r="M1414" s="2" t="n">
-        <v>340.09</v>
+        <v>245.21</v>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>1432083-2331-CM26</t>
+          <t>1432083-2330-CM26</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
@@ -92418,13 +92418,13 @@
         </is>
       </c>
       <c r="M1415" s="2" t="n">
-        <v>314.67</v>
+        <v>235.7</v>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>1432083-2330-CM26</t>
+          <t>1432083-2331-CM26</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
@@ -92483,7 +92483,7 @@
         </is>
       </c>
       <c r="M1416" s="2" t="n">
-        <v>235.7</v>
+        <v>314.67</v>
       </c>
     </row>
     <row r="1417">
@@ -92619,7 +92619,7 @@
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>5418-229-CM26</t>
+          <t>5612-188-CM26</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
@@ -92639,17 +92639,17 @@
       </c>
       <c r="E1419" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1419" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G1419" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H1419" t="inlineStr">
@@ -92678,13 +92678,13 @@
         </is>
       </c>
       <c r="M1419" s="2" t="n">
-        <v>1720.64</v>
+        <v>413.25</v>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>5612-188-CM26</t>
+          <t>5418-229-CM26</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
@@ -92704,17 +92704,17 @@
       </c>
       <c r="E1420" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1420" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G1420" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1420" t="inlineStr">
@@ -92743,13 +92743,13 @@
         </is>
       </c>
       <c r="M1420" s="2" t="n">
-        <v>413.25</v>
+        <v>1720.64</v>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>1305560-85-CM26</t>
+          <t>1305560-84-CM26</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
@@ -92789,12 +92789,12 @@
       </c>
       <c r="I1421" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1421" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1421" t="inlineStr">
@@ -92808,13 +92808,13 @@
         </is>
       </c>
       <c r="M1421" s="2" t="n">
-        <v>396.44</v>
+        <v>83.20999999999999</v>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>1305560-84-CM26</t>
+          <t>1305560-85-CM26</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
@@ -92854,12 +92854,12 @@
       </c>
       <c r="I1422" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1422" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1422" t="inlineStr">
@@ -92873,7 +92873,7 @@
         </is>
       </c>
       <c r="M1422" s="2" t="n">
-        <v>83.20999999999999</v>
+        <v>396.44</v>
       </c>
     </row>
     <row r="1423">
@@ -92944,7 +92944,7 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>620039-21-CM26</t>
+          <t>2180-173-CM26</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
@@ -92964,17 +92964,17 @@
       </c>
       <c r="E1424" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1424" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1424" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1424" t="inlineStr">
@@ -93003,13 +93003,13 @@
         </is>
       </c>
       <c r="M1424" s="2" t="n">
-        <v>210.68</v>
+        <v>203.35</v>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>2905-711-CM26</t>
+          <t>620039-21-CM26</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
@@ -93034,12 +93034,12 @@
       </c>
       <c r="F1425" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G1425" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H1425" t="inlineStr">
@@ -93049,12 +93049,12 @@
       </c>
       <c r="I1425" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1425" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1425" t="inlineStr">
@@ -93068,13 +93068,13 @@
         </is>
       </c>
       <c r="M1425" s="2" t="n">
-        <v>607.26</v>
+        <v>210.68</v>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>2180-173-CM26</t>
+          <t>2905-711-CM26</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
@@ -93094,17 +93094,17 @@
       </c>
       <c r="E1426" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1426" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G1426" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H1426" t="inlineStr">
@@ -93114,12 +93114,12 @@
       </c>
       <c r="I1426" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1426" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1426" t="inlineStr">
@@ -93133,13 +93133,13 @@
         </is>
       </c>
       <c r="M1426" s="2" t="n">
-        <v>203.35</v>
+        <v>607.26</v>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>1271-44-CM26</t>
+          <t>5418-233-CM26</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
@@ -93164,12 +93164,12 @@
       </c>
       <c r="F1427" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G1427" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1427" t="inlineStr">
@@ -93198,13 +93198,13 @@
         </is>
       </c>
       <c r="M1427" s="2" t="n">
-        <v>126.18</v>
+        <v>265.32</v>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>5418-233-CM26</t>
+          <t>1271-44-CM26</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
@@ -93229,12 +93229,12 @@
       </c>
       <c r="F1428" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G1428" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H1428" t="inlineStr">
@@ -93263,7 +93263,7 @@
         </is>
       </c>
       <c r="M1428" s="2" t="n">
-        <v>265.32</v>
+        <v>126.18</v>
       </c>
     </row>
     <row r="1429">
@@ -93789,7 +93789,7 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>1340-549-CM26</t>
+          <t>1035685-341-CM26</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
@@ -93814,12 +93814,12 @@
       </c>
       <c r="F1437" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G1437" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1437" t="inlineStr">
@@ -93848,13 +93848,13 @@
         </is>
       </c>
       <c r="M1437" s="2" t="n">
-        <v>127.75</v>
+        <v>84.65000000000001</v>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>1035685-341-CM26</t>
+          <t>1340-549-CM26</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
@@ -93879,12 +93879,12 @@
       </c>
       <c r="F1438" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G1438" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H1438" t="inlineStr">
@@ -93913,13 +93913,13 @@
         </is>
       </c>
       <c r="M1438" s="2" t="n">
-        <v>84.65000000000001</v>
+        <v>127.75</v>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>299-199-CM26</t>
+          <t>299-200-CM26</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
@@ -93978,13 +93978,13 @@
         </is>
       </c>
       <c r="M1439" s="2" t="n">
-        <v>3213.33</v>
+        <v>755.3</v>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>299-200-CM26</t>
+          <t>299-199-CM26</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
@@ -94043,7 +94043,7 @@
         </is>
       </c>
       <c r="M1440" s="2" t="n">
-        <v>755.3</v>
+        <v>3213.33</v>
       </c>
     </row>
     <row r="1441">
@@ -94374,7 +94374,7 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>5740-381-CM26</t>
+          <t>1208106-80-CM26</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
@@ -94394,17 +94394,17 @@
       </c>
       <c r="E1446" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1446" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G1446" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H1446" t="inlineStr">
@@ -94433,13 +94433,13 @@
         </is>
       </c>
       <c r="M1446" s="2" t="n">
-        <v>658.87</v>
+        <v>198.3</v>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>1208106-79-CM26</t>
+          <t>5740-381-CM26</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
@@ -94464,12 +94464,12 @@
       </c>
       <c r="F1447" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G1447" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1447" t="inlineStr">
@@ -94479,12 +94479,12 @@
       </c>
       <c r="I1447" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1447" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1447" t="inlineStr">
@@ -94498,13 +94498,13 @@
         </is>
       </c>
       <c r="M1447" s="2" t="n">
-        <v>231.7</v>
+        <v>658.87</v>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>1208106-80-CM26</t>
+          <t>926853-85-CM26</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
@@ -94529,12 +94529,12 @@
       </c>
       <c r="F1448" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G1448" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1448" t="inlineStr">
@@ -94544,12 +94544,12 @@
       </c>
       <c r="I1448" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1448" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1448" t="inlineStr">
@@ -94563,13 +94563,13 @@
         </is>
       </c>
       <c r="M1448" s="2" t="n">
-        <v>198.3</v>
+        <v>106.17</v>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>5742-178-CM26</t>
+          <t>1208106-79-CM26</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
@@ -94589,17 +94589,17 @@
       </c>
       <c r="E1449" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1449" t="inlineStr">
         <is>
-          <t>61.979.040-5</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G1449" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H1449" t="inlineStr">
@@ -94628,13 +94628,13 @@
         </is>
       </c>
       <c r="M1449" s="2" t="n">
-        <v>308.72</v>
+        <v>231.7</v>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>5612-197-CM26</t>
+          <t>5742-178-CM26</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
@@ -94654,17 +94654,17 @@
       </c>
       <c r="E1450" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1450" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.979.040-5</t>
         </is>
       </c>
       <c r="G1450" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H1450" t="inlineStr">
@@ -94693,13 +94693,13 @@
         </is>
       </c>
       <c r="M1450" s="2" t="n">
-        <v>206.14</v>
+        <v>308.72</v>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>926853-85-CM26</t>
+          <t>5612-197-CM26</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
@@ -94719,17 +94719,17 @@
       </c>
       <c r="E1451" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1451" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G1451" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H1451" t="inlineStr">
@@ -94758,7 +94758,7 @@
         </is>
       </c>
       <c r="M1451" s="2" t="n">
-        <v>106.17</v>
+        <v>206.14</v>
       </c>
     </row>
     <row r="1452">
@@ -95089,7 +95089,7 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>5751-274-CM26</t>
+          <t>5740-383-CM26</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
@@ -95114,12 +95114,12 @@
       </c>
       <c r="F1457" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G1457" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1457" t="inlineStr">
@@ -95129,12 +95129,12 @@
       </c>
       <c r="I1457" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1457" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1457" t="inlineStr">
@@ -95148,7 +95148,7 @@
         </is>
       </c>
       <c r="M1457" s="2" t="n">
-        <v>207.94</v>
+        <v>195.02</v>
       </c>
     </row>
     <row r="1458">
@@ -95219,7 +95219,7 @@
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>5740-383-CM26</t>
+          <t>5751-274-CM26</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
@@ -95244,12 +95244,12 @@
       </c>
       <c r="F1459" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G1459" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H1459" t="inlineStr">
@@ -95259,12 +95259,12 @@
       </c>
       <c r="I1459" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1459" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1459" t="inlineStr">
@@ -95278,7 +95278,7 @@
         </is>
       </c>
       <c r="M1459" s="2" t="n">
-        <v>195.02</v>
+        <v>207.94</v>
       </c>
     </row>
     <row r="1460">
@@ -95349,7 +95349,7 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>1035685-364-CM26</t>
+          <t>2180-199-CM26</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
@@ -95374,12 +95374,12 @@
       </c>
       <c r="F1461" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1461" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1461" t="inlineStr">
@@ -95408,13 +95408,13 @@
         </is>
       </c>
       <c r="M1461" s="2" t="n">
-        <v>112.78</v>
+        <v>466.08</v>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>2180-199-CM26</t>
+          <t>1035685-362-CM26</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
@@ -95439,12 +95439,12 @@
       </c>
       <c r="F1462" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G1462" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1462" t="inlineStr">
@@ -95473,13 +95473,13 @@
         </is>
       </c>
       <c r="M1462" s="2" t="n">
-        <v>466.08</v>
+        <v>99.95</v>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>1035685-362-CM26</t>
+          <t>5740-384-CM26</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
@@ -95504,12 +95504,12 @@
       </c>
       <c r="F1463" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G1463" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1463" t="inlineStr">
@@ -95519,12 +95519,12 @@
       </c>
       <c r="I1463" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1463" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1463" t="inlineStr">
@@ -95538,13 +95538,13 @@
         </is>
       </c>
       <c r="M1463" s="2" t="n">
-        <v>99.95</v>
+        <v>195.61</v>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>5740-384-CM26</t>
+          <t>1035685-364-CM26</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
@@ -95569,12 +95569,12 @@
       </c>
       <c r="F1464" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G1464" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1464" t="inlineStr">
@@ -95584,12 +95584,12 @@
       </c>
       <c r="I1464" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1464" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1464" t="inlineStr">
@@ -95603,13 +95603,13 @@
         </is>
       </c>
       <c r="M1464" s="2" t="n">
-        <v>195.61</v>
+        <v>112.78</v>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>5418-252-CM26</t>
+          <t>5418-250-CM26</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
@@ -95649,12 +95649,12 @@
       </c>
       <c r="I1465" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1465" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1465" t="inlineStr">
@@ -95668,13 +95668,13 @@
         </is>
       </c>
       <c r="M1465" s="2" t="n">
-        <v>152</v>
+        <v>194.89</v>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>5418-251-CM26</t>
+          <t>5418-249-CM26</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
@@ -95714,12 +95714,12 @@
       </c>
       <c r="I1466" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1466" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1466" t="inlineStr">
@@ -95733,13 +95733,13 @@
         </is>
       </c>
       <c r="M1466" s="2" t="n">
-        <v>226.24</v>
+        <v>312.4</v>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>5418-248-CM26</t>
+          <t>5418-252-CM26</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
@@ -95779,12 +95779,12 @@
       </c>
       <c r="I1467" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1467" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1467" t="inlineStr">
@@ -95798,13 +95798,13 @@
         </is>
       </c>
       <c r="M1467" s="2" t="n">
-        <v>205.57</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>5418-249-CM26</t>
+          <t>5418-251-CM26</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
@@ -95844,12 +95844,12 @@
       </c>
       <c r="I1468" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1468" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1468" t="inlineStr">
@@ -95863,13 +95863,13 @@
         </is>
       </c>
       <c r="M1468" s="2" t="n">
-        <v>312.4</v>
+        <v>226.24</v>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>5418-250-CM26</t>
+          <t>5418-248-CM26</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
@@ -95928,7 +95928,7 @@
         </is>
       </c>
       <c r="M1469" s="2" t="n">
-        <v>194.89</v>
+        <v>205.57</v>
       </c>
     </row>
     <row r="1470">
@@ -95999,7 +95999,7 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>2180-204-CM26</t>
+          <t>2180-203-CM26</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
@@ -96058,13 +96058,13 @@
         </is>
       </c>
       <c r="M1471" s="2" t="n">
-        <v>161.35</v>
+        <v>223.42</v>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>2180-205-CM26</t>
+          <t>2180-204-CM26</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
@@ -96104,12 +96104,12 @@
       </c>
       <c r="I1472" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J1472" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K1472" t="inlineStr">
@@ -96123,13 +96123,13 @@
         </is>
       </c>
       <c r="M1472" s="2" t="n">
-        <v>114.58</v>
+        <v>161.35</v>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>1208106-82-CM26</t>
+          <t>2180-205-CM26</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
@@ -96149,17 +96149,17 @@
       </c>
       <c r="E1473" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1473" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G1473" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H1473" t="inlineStr">
@@ -96169,12 +96169,12 @@
       </c>
       <c r="I1473" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J1473" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K1473" t="inlineStr">
@@ -96188,13 +96188,13 @@
         </is>
       </c>
       <c r="M1473" s="2" t="n">
-        <v>883.2</v>
+        <v>114.58</v>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>1208106-83-CM26</t>
+          <t>1208106-82-CM26</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
@@ -96253,13 +96253,13 @@
         </is>
       </c>
       <c r="M1474" s="2" t="n">
-        <v>234.55</v>
+        <v>883.2</v>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>926853-86-CM26</t>
+          <t>1208106-83-CM26</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
@@ -96279,17 +96279,17 @@
       </c>
       <c r="E1475" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1475" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G1475" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H1475" t="inlineStr">
@@ -96318,13 +96318,13 @@
         </is>
       </c>
       <c r="M1475" s="2" t="n">
-        <v>200.63</v>
+        <v>234.55</v>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>1422032-125-CM26</t>
+          <t>926853-86-CM26</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
@@ -96349,12 +96349,12 @@
       </c>
       <c r="F1476" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G1476" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H1476" t="inlineStr">
@@ -96383,13 +96383,13 @@
         </is>
       </c>
       <c r="M1476" s="2" t="n">
-        <v>150.21</v>
+        <v>200.63</v>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>1422032-126-CM26</t>
+          <t>1422032-125-CM26</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
@@ -96454,7 +96454,7 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>2180-203-CM26</t>
+          <t>1422032-126-CM26</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
@@ -96479,12 +96479,12 @@
       </c>
       <c r="F1478" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G1478" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H1478" t="inlineStr">
@@ -96513,7 +96513,7 @@
         </is>
       </c>
       <c r="M1478" s="2" t="n">
-        <v>223.42</v>
+        <v>150.21</v>
       </c>
     </row>
     <row r="1479">
@@ -96904,6 +96904,136 @@
       </c>
       <c r="M1484" s="2" t="n">
         <v>265.17</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>2027-101-CM26</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F1485" t="inlineStr">
+        <is>
+          <t>60.902.015-6</t>
+        </is>
+      </c>
+      <c r="G1485" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+        </is>
+      </c>
+      <c r="H1485" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I1485" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J1485" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K1485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L1485" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M1485" s="2" t="n">
+        <v>319.24</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>1340-603-CM26</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F1486" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G1486" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H1486" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I1486" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J1486" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K1486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L1486" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M1486" s="2" t="n">
+        <v>353.77</v>
       </c>
     </row>
   </sheetData>
